--- a/Faculty_2026_2027.xlsx
+++ b/Faculty_2026_2027.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajayj\Downloads\feedback\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\feedback_form\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3BDF05-C96A-49E1-A2C7-3A9DA3A672DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEFDA03-EBE2-4B5D-9ECB-7AADB6B9CEF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{697950EC-CD97-4070-9CAF-A42882262331}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{697950EC-CD97-4070-9CAF-A42882262331}"/>
   </bookViews>
   <sheets>
     <sheet name="Faculty_Details" sheetId="1" r:id="rId1"/>
@@ -2462,9 +2462,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2502,7 +2502,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2608,7 +2608,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2750,7 +2750,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2759,22 +2759,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97249C7C-A7D1-4BDD-AEA7-89ACEB0BD2E6}">
   <dimension ref="A1:J320"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.21875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="11" customWidth="1"/>
-    <col min="3" max="3" width="35.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" style="11" customWidth="1"/>
     <col min="5" max="5" width="12" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.77734375" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.33203125" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.21875" style="25" customWidth="1"/>
-    <col min="9" max="9" width="21.21875" style="11" customWidth="1"/>
-    <col min="10" max="10" width="57.5546875" style="11" customWidth="1"/>
-    <col min="11" max="16384" width="9.21875" style="11"/>
+    <col min="6" max="6" width="14.81640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.36328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.1796875" style="25" customWidth="1"/>
+    <col min="9" max="9" width="21.1796875" style="11" customWidth="1"/>
+    <col min="10" max="10" width="57.54296875" style="11" customWidth="1"/>
+    <col min="11" max="16384" width="9.1796875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="46" t="s">
         <v>684</v>
       </c>
@@ -2787,7 +2787,7 @@
       <c r="H1" s="46"/>
       <c r="I1" s="46"/>
     </row>
-    <row r="2" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="47" t="s">
         <v>691</v>
       </c>
@@ -2800,7 +2800,7 @@
       <c r="H2" s="47"/>
       <c r="I2" s="47"/>
     </row>
-    <row r="3" spans="1:10" s="22" customFormat="1" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="22" customFormat="1" ht="35.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>0</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -2945,22 +2945,22 @@
         <v>40</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>50</v>
+        <v>668</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>48</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="8">
-        <v>37795</v>
+      <c r="I7" s="17">
+        <v>45096</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -2977,22 +2977,22 @@
         <v>40</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>48</v>
+        <v>667</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="17">
-        <v>45096</v>
+      <c r="I8" s="8">
+        <v>37795</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -3140,19 +3140,19 @@
         <v>667</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="27" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="I13" s="16">
-        <v>36538</v>
+        <v>36539</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -3172,19 +3172,19 @@
         <v>667</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>15</v>
       </c>
       <c r="I14" s="16">
-        <v>36539</v>
+        <v>36538</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -3620,19 +3620,19 @@
         <v>667</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="I28" s="16">
-        <v>39378</v>
+        <v>41078</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -3643,28 +3643,28 @@
         <v>576</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="G29" s="27" t="s">
-        <v>589</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I29" s="15">
-        <v>40345</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>581</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I29" s="16">
+        <v>42173</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -3675,28 +3675,28 @@
         <v>576</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="G30" s="33" t="s">
-        <v>590</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I30" s="26">
-        <v>40710</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>582</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="16">
+        <v>39378</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -3715,20 +3715,20 @@
       <c r="F31" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="G31" s="28" t="s">
-        <v>580</v>
+      <c r="G31" s="34" t="s">
+        <v>583</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I31" s="16">
-        <v>41078</v>
+        <v>43269</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -3748,19 +3748,19 @@
         <v>667</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I32" s="16">
-        <v>42173</v>
+        <v>43374</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -3779,20 +3779,20 @@
       <c r="F33" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="G33" s="34" t="s">
-        <v>583</v>
+      <c r="G33" s="28" t="s">
+        <v>585</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I33" s="16">
-        <v>43269</v>
+      <c r="I33" s="8">
+        <v>43633</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -3803,28 +3803,28 @@
         <v>576</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="G34" s="27" t="s">
-        <v>591</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I34" s="15">
-        <v>43269</v>
+        <v>9</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>586</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I34" s="8">
+        <v>44417</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -3844,19 +3844,19 @@
         <v>667</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I35" s="16">
-        <v>43374</v>
+        <v>46189</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -3876,19 +3876,19 @@
         <v>667</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I36" s="8">
-        <v>43633</v>
+      <c r="I36" s="19">
+        <v>46190</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -3899,28 +3899,28 @@
         <v>576</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="G37" s="28" t="s">
-        <v>586</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I37" s="8">
-        <v>44417</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="G37" s="27" t="s">
+        <v>589</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I37" s="15">
+        <v>40345</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -3937,22 +3937,22 @@
         <v>40</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="G38" s="27" t="s">
-        <v>592</v>
+        <v>667</v>
+      </c>
+      <c r="G38" s="33" t="s">
+        <v>590</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I38" s="15">
-        <v>44760</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I38" s="26">
+        <v>40710</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -3969,22 +3969,22 @@
         <v>40</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G39" s="27" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I39" s="15">
-        <v>44760</v>
+        <v>43269</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -4001,22 +4001,22 @@
         <v>40</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G40" s="27" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I40" s="8">
-        <v>45096</v>
+      <c r="I40" s="15">
+        <v>44760</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -4033,22 +4033,22 @@
         <v>40</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G41" s="27" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I41" s="8">
-        <v>45096</v>
+      <c r="I41" s="15">
+        <v>44760</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -4065,10 +4065,10 @@
         <v>40</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G42" s="27" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>53</v>
@@ -4077,10 +4077,10 @@
         <v>45096</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>667</v>
       </c>
       <c r="G43" s="27" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>53</v>
@@ -4109,10 +4109,10 @@
         <v>45096</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -4123,28 +4123,28 @@
         <v>576</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="G44" s="28" t="s">
-        <v>587</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I44" s="16">
-        <v>46189</v>
+        <v>39</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="G44" s="27" t="s">
+        <v>596</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I44" s="8">
+        <v>45096</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -4155,28 +4155,28 @@
         <v>576</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>667</v>
-      </c>
-      <c r="G45" s="28" t="s">
-        <v>588</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I45" s="19">
-        <v>46190</v>
+        <v>39</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>597</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I45" s="8">
+        <v>45096</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -4289,22 +4289,22 @@
         <v>40</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="G49" s="27" t="s">
-        <v>601</v>
+        <v>668</v>
+      </c>
+      <c r="G49" s="33" t="s">
+        <v>599</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I49" s="8">
-        <v>38882</v>
+        <v>40707</v>
       </c>
       <c r="J49" s="27" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -4321,22 +4321,22 @@
         <v>40</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="G50" s="33" t="s">
-        <v>599</v>
+        <v>667</v>
+      </c>
+      <c r="G50" s="27" t="s">
+        <v>601</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I50" s="8">
-        <v>40707</v>
+        <v>38882</v>
       </c>
       <c r="J50" s="27" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="60" spans="1:10" s="25" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="23" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="23" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="23" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="23" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="23" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="23" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="23" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -5136,7 +5136,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>104</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>10</v>
@@ -5155,20 +5155,20 @@
       <c r="F76" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G76" s="28" t="s">
-        <v>127</v>
+      <c r="G76" s="38" t="s">
+        <v>105</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I76" s="8">
-        <v>40345</v>
+        <v>41078</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -5187,20 +5187,20 @@
       <c r="F77" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G77" s="38" t="s">
-        <v>105</v>
+      <c r="G77" s="28" t="s">
+        <v>107</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="I77" s="8">
-        <v>41078</v>
+        <v>41445</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -5211,28 +5211,28 @@
         <v>104</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G78" s="38" t="s">
-        <v>129</v>
+      <c r="G78" s="28" t="s">
+        <v>109</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I78" s="8">
-        <v>41078</v>
+        <v>42537</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -5252,19 +5252,19 @@
         <v>667</v>
       </c>
       <c r="G79" s="28" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I79" s="8">
-        <v>41445</v>
+        <v>42982</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -5284,19 +5284,19 @@
         <v>667</v>
       </c>
       <c r="G80" s="28" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I80" s="8">
-        <v>42537</v>
+        <v>44417</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -5316,19 +5316,19 @@
         <v>667</v>
       </c>
       <c r="G81" s="28" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I81" s="8">
-        <v>42982</v>
+        <v>45096</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -5348,19 +5348,19 @@
         <v>667</v>
       </c>
       <c r="G82" s="28" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I82" s="8">
-        <v>44417</v>
+        <v>45097</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -5377,22 +5377,22 @@
         <v>10</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G83" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="H83" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H83" s="27" t="s">
         <v>53</v>
       </c>
       <c r="I83" s="8">
-        <v>45096</v>
+        <v>45462</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -5409,22 +5409,22 @@
         <v>10</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G84" s="28" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I84" s="8">
-        <v>45097</v>
+        <v>45463</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -5435,28 +5435,28 @@
         <v>104</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G85" s="28" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I85" s="8">
-        <v>45096</v>
+        <v>45505</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -5467,28 +5467,28 @@
         <v>104</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>668</v>
       </c>
       <c r="G86" s="28" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I86" s="8">
-        <v>45096</v>
+        <v>45825</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -5502,25 +5502,25 @@
         <v>39</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G87" s="28" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I87" s="8">
-        <v>45096</v>
+        <v>40345</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -5531,28 +5531,28 @@
         <v>104</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="G88" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="H88" s="27" t="s">
+        <v>667</v>
+      </c>
+      <c r="G88" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="H88" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I88" s="8">
-        <v>45462</v>
+        <v>41078</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -5563,28 +5563,28 @@
         <v>104</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>668</v>
       </c>
       <c r="G89" s="28" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I89" s="8">
-        <v>45463</v>
+        <v>45096</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -5595,28 +5595,28 @@
         <v>104</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G90" s="28" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I90" s="8">
-        <v>45505</v>
+        <v>45096</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -5633,22 +5633,22 @@
         <v>40</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G91" s="28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I91" s="8">
-        <v>45462</v>
+        <v>45096</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -5659,28 +5659,28 @@
         <v>104</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G92" s="28" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I92" s="8">
-        <v>45825</v>
+        <v>45462</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -5697,10 +5697,10 @@
         <v>40</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G93" s="28" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>53</v>
@@ -5709,10 +5709,10 @@
         <v>45824</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -5729,10 +5729,10 @@
         <v>40</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G94" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>53</v>
@@ -5741,10 +5741,10 @@
         <v>45824</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -5808,7 +5808,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -5891,20 +5891,20 @@
       <c r="F99" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G99" s="28" t="s">
-        <v>155</v>
+      <c r="G99" s="38" t="s">
+        <v>152</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="I99" s="8">
-        <v>44075</v>
+        <v>45446</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -5924,19 +5924,19 @@
         <v>667</v>
       </c>
       <c r="G100" s="28" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I100" s="8">
-        <v>44417</v>
+        <v>44075</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -5953,10 +5953,10 @@
         <v>40</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G101" s="28" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>53</v>
@@ -5965,10 +5965,10 @@
         <v>44417</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -5985,22 +5985,22 @@
         <v>40</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="G102" s="38" t="s">
-        <v>152</v>
+        <v>668</v>
+      </c>
+      <c r="G102" s="28" t="s">
+        <v>159</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="I102" s="8">
-        <v>45446</v>
+        <v>44417</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -6051,20 +6051,20 @@
       <c r="F104" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G104" s="28" t="s">
-        <v>166</v>
+      <c r="G104" s="38" t="s">
+        <v>164</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I104" s="8">
-        <v>36327</v>
+        <v>40707</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -6083,20 +6083,20 @@
       <c r="F105" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G105" s="38" t="s">
-        <v>164</v>
+      <c r="G105" s="28" t="s">
+        <v>166</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>53</v>
       </c>
       <c r="I105" s="8">
-        <v>40707</v>
+        <v>36327</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -6128,7 +6128,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -6177,10 +6177,10 @@
         <v>40</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G108" s="28" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H108" s="4" t="s">
         <v>53</v>
@@ -6189,10 +6189,10 @@
         <v>41078</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -6209,10 +6209,10 @@
         <v>40</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G109" s="28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>53</v>
@@ -6221,10 +6221,10 @@
         <v>41078</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>107</v>
       </c>
@@ -6256,7 +6256,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>108</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>109</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>110</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>111</v>
       </c>
@@ -6384,7 +6384,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>112</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>113</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>114</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>115</v>
       </c>
@@ -6491,28 +6491,28 @@
         <v>184</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>667</v>
       </c>
       <c r="G118" s="27" t="s">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I118" s="15">
-        <v>37788</v>
+        <v>12</v>
+      </c>
+      <c r="I118" s="8">
+        <v>38985</v>
       </c>
       <c r="J118" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>116</v>
       </c>
@@ -6523,28 +6523,28 @@
         <v>184</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>668</v>
       </c>
       <c r="G119" s="27" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I119" s="8">
-        <v>38882</v>
+        <v>39373</v>
       </c>
       <c r="J119" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>117</v>
       </c>
@@ -6564,19 +6564,19 @@
         <v>667</v>
       </c>
       <c r="G120" s="27" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>12</v>
       </c>
       <c r="I120" s="8">
-        <v>38985</v>
+        <v>39398</v>
       </c>
       <c r="J120" s="7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>118</v>
       </c>
@@ -6593,22 +6593,22 @@
         <v>10</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G121" s="27" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="I121" s="8">
-        <v>39373</v>
+        <v>39399</v>
       </c>
       <c r="J121" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>119</v>
       </c>
@@ -6625,22 +6625,22 @@
         <v>10</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G122" s="27" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="I122" s="8">
-        <v>39398</v>
+        <v>41078</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>120</v>
       </c>
@@ -6660,19 +6660,19 @@
         <v>667</v>
       </c>
       <c r="G123" s="27" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="I123" s="8">
-        <v>39399</v>
+        <v>41445</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>121</v>
       </c>
@@ -6689,22 +6689,22 @@
         <v>10</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G124" s="27" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I124" s="8">
-        <v>41078</v>
+        <v>41446</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>122</v>
       </c>
@@ -6721,22 +6721,22 @@
         <v>10</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G125" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="H125" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="H125" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I125" s="8">
-        <v>41465</v>
+        <v>41447</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>123</v>
       </c>
@@ -6756,19 +6756,19 @@
         <v>667</v>
       </c>
       <c r="G126" s="27" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I126" s="8">
-        <v>41445</v>
+        <v>41463</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>124</v>
       </c>
@@ -6785,22 +6785,22 @@
         <v>10</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G127" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="H127" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H127" s="27" t="s">
         <v>53</v>
       </c>
       <c r="I127" s="8">
-        <v>41446</v>
+        <v>41465</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" s="23" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>125</v>
       </c>
@@ -6817,22 +6817,22 @@
         <v>10</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G128" s="27" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I128" s="8">
-        <v>41447</v>
+        <v>43269</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>126</v>
       </c>
@@ -6852,19 +6852,19 @@
         <v>667</v>
       </c>
       <c r="G129" s="27" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I129" s="8">
-        <v>41463</v>
+        <v>43270</v>
       </c>
       <c r="J129" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>127</v>
       </c>
@@ -6881,22 +6881,22 @@
         <v>10</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G130" s="27" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I130" s="8">
-        <v>43269</v>
+      <c r="I130" s="18">
+        <v>43633</v>
       </c>
       <c r="J130" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>128</v>
       </c>
@@ -6916,19 +6916,19 @@
         <v>667</v>
       </c>
       <c r="G131" s="27" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I131" s="8">
-        <v>43270</v>
+        <v>44417</v>
       </c>
       <c r="J131" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>129</v>
       </c>
@@ -6948,19 +6948,19 @@
         <v>667</v>
       </c>
       <c r="G132" s="27" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I132" s="18">
-        <v>43633</v>
+      <c r="I132" s="8">
+        <v>44762</v>
       </c>
       <c r="J132" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>130</v>
       </c>
@@ -6971,28 +6971,28 @@
         <v>184</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>667</v>
       </c>
       <c r="G133" s="27" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I133" s="8">
-        <v>44417</v>
+      <c r="I133" s="15">
+        <v>37788</v>
       </c>
       <c r="J133" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" s="23" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>131</v>
       </c>
@@ -7003,28 +7003,28 @@
         <v>184</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G134" s="27" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I134" s="8">
-        <v>44762</v>
+        <v>38882</v>
       </c>
       <c r="J134" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>132</v>
       </c>
@@ -7041,10 +7041,10 @@
         <v>40</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G135" s="27" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>53</v>
@@ -7053,10 +7053,10 @@
         <v>44760</v>
       </c>
       <c r="J135" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>133</v>
       </c>
@@ -7076,7 +7076,7 @@
         <v>668</v>
       </c>
       <c r="G136" s="27" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>53</v>
@@ -7085,10 +7085,10 @@
         <v>44760</v>
       </c>
       <c r="J136" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>134</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>668</v>
       </c>
       <c r="G137" s="27" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>53</v>
@@ -7117,10 +7117,10 @@
         <v>44760</v>
       </c>
       <c r="J137" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>135</v>
       </c>
@@ -7137,10 +7137,10 @@
         <v>40</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G138" s="27" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>53</v>
@@ -7149,10 +7149,10 @@
         <v>44760</v>
       </c>
       <c r="J138" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>136</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>137</v>
       </c>
@@ -7216,7 +7216,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>138</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>139</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>140</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>141</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>142</v>
       </c>
@@ -7376,7 +7376,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>143</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>144</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>145</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>146</v>
       </c>
@@ -7504,7 +7504,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>147</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>148</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>149</v>
       </c>
@@ -7600,7 +7600,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>150</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>151</v>
       </c>
@@ -7643,28 +7643,28 @@
         <v>244</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G154" s="28" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="I154" s="8">
-        <v>39603</v>
+        <v>41078</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>152</v>
       </c>
@@ -7675,28 +7675,28 @@
         <v>244</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G155" s="28" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I155" s="8">
-        <v>39603</v>
+        <v>41207</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>153</v>
       </c>
@@ -7707,28 +7707,28 @@
         <v>244</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>667</v>
       </c>
       <c r="G156" s="28" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="I156" s="8">
-        <v>41078</v>
+        <v>41445</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>154</v>
       </c>
@@ -7739,28 +7739,28 @@
         <v>244</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>667</v>
       </c>
       <c r="G157" s="28" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="I157" s="8">
-        <v>41078</v>
+        <v>41446</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>155</v>
       </c>
@@ -7777,22 +7777,22 @@
         <v>10</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G158" s="28" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I158" s="8">
-        <v>41078</v>
+        <v>41447</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>156</v>
       </c>
@@ -7812,19 +7812,19 @@
         <v>668</v>
       </c>
       <c r="G159" s="28" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="I159" s="8">
-        <v>41207</v>
+        <v>41449</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>157</v>
       </c>
@@ -7841,22 +7841,22 @@
         <v>10</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G160" s="28" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I160" s="8">
-        <v>41449</v>
+        <v>41450</v>
       </c>
       <c r="J160" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>158</v>
       </c>
@@ -7876,19 +7876,19 @@
         <v>667</v>
       </c>
       <c r="G161" s="28" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I161" s="8">
-        <v>41445</v>
+        <v>42537</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>159</v>
       </c>
@@ -7905,22 +7905,22 @@
         <v>10</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G162" s="28" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I162" s="8">
-        <v>41446</v>
+        <v>44417</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>160</v>
       </c>
@@ -7940,19 +7940,19 @@
         <v>667</v>
       </c>
       <c r="G163" s="28" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I163" s="8">
-        <v>41447</v>
+        <v>45096</v>
       </c>
       <c r="J163" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>161</v>
       </c>
@@ -7972,19 +7972,19 @@
         <v>667</v>
       </c>
       <c r="G164" s="28" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I164" s="8">
-        <v>41450</v>
+        <v>45097</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>162</v>
       </c>
@@ -8016,7 +8016,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>163</v>
       </c>
@@ -8036,19 +8036,19 @@
         <v>667</v>
       </c>
       <c r="G166" s="28" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I166" s="8">
-        <v>42173</v>
+        <v>39603</v>
       </c>
       <c r="J166" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>164</v>
       </c>
@@ -8059,28 +8059,28 @@
         <v>244</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>667</v>
       </c>
       <c r="G167" s="28" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I167" s="8">
-        <v>42537</v>
+        <v>39603</v>
       </c>
       <c r="J167" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>165</v>
       </c>
@@ -8100,19 +8100,19 @@
         <v>667</v>
       </c>
       <c r="G168" s="28" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I168" s="8">
-        <v>42537</v>
+        <v>41078</v>
       </c>
       <c r="J168" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>166</v>
       </c>
@@ -8132,19 +8132,19 @@
         <v>667</v>
       </c>
       <c r="G169" s="28" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I169" s="8">
-        <v>42537</v>
+        <v>41078</v>
       </c>
       <c r="J169" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>167</v>
       </c>
@@ -8155,28 +8155,28 @@
         <v>244</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G170" s="28" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I170" s="8">
-        <v>44417</v>
+        <v>42173</v>
       </c>
       <c r="J170" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>168</v>
       </c>
@@ -8193,22 +8193,22 @@
         <v>40</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G171" s="28" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I171" s="8">
-        <v>44760</v>
+        <v>42537</v>
       </c>
       <c r="J171" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>169</v>
       </c>
@@ -8228,19 +8228,19 @@
         <v>667</v>
       </c>
       <c r="G172" s="28" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I172" s="8">
-        <v>44760</v>
+        <v>42537</v>
       </c>
       <c r="J172" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>170</v>
       </c>
@@ -8260,7 +8260,7 @@
         <v>667</v>
       </c>
       <c r="G173" s="28" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>26</v>
@@ -8269,10 +8269,10 @@
         <v>44760</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>171</v>
       </c>
@@ -8283,28 +8283,28 @@
         <v>244</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>667</v>
       </c>
       <c r="G174" s="28" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I174" s="8">
-        <v>45096</v>
+        <v>44760</v>
       </c>
       <c r="J174" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>172</v>
       </c>
@@ -8315,28 +8315,28 @@
         <v>244</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G175" s="28" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="I175" s="8">
-        <v>45097</v>
+        <v>44760</v>
       </c>
       <c r="J175" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>173</v>
       </c>
@@ -8368,7 +8368,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>174</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>175</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>176</v>
       </c>
@@ -8464,7 +8464,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>177</v>
       </c>
@@ -8496,7 +8496,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>178</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>179</v>
       </c>
@@ -8560,7 +8560,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>180</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>181</v>
       </c>
@@ -8624,7 +8624,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>182</v>
       </c>
@@ -8656,7 +8656,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>183</v>
       </c>
@@ -8675,8 +8675,8 @@
       <c r="F186" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="G186" s="1" t="s">
-        <v>613</v>
+      <c r="G186" s="45" t="s">
+        <v>614</v>
       </c>
       <c r="H186" s="4" t="s">
         <v>53</v>
@@ -8685,10 +8685,10 @@
         <v>41078</v>
       </c>
       <c r="J186" s="31" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>184</v>
       </c>
@@ -8707,8 +8707,8 @@
       <c r="F187" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="G187" s="45" t="s">
-        <v>614</v>
+      <c r="G187" s="1" t="s">
+        <v>613</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>53</v>
@@ -8717,10 +8717,10 @@
         <v>41078</v>
       </c>
       <c r="J187" s="31" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>185</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>186</v>
       </c>
@@ -8784,7 +8784,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>187</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>188</v>
       </c>
@@ -8848,7 +8848,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>189</v>
       </c>
@@ -8880,7 +8880,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>190</v>
       </c>
@@ -8899,20 +8899,20 @@
       <c r="F193" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G193" s="34" t="s">
-        <v>329</v>
+      <c r="G193" s="40" t="s">
+        <v>331</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>12</v>
       </c>
       <c r="I193" s="8">
-        <v>36941</v>
+        <v>39373</v>
       </c>
       <c r="J193" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>191</v>
       </c>
@@ -8923,28 +8923,28 @@
         <v>328</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G194" s="27" t="s">
-        <v>351</v>
+      <c r="G194" s="34" t="s">
+        <v>329</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I194" s="16">
-        <v>37795</v>
+        <v>12</v>
+      </c>
+      <c r="I194" s="8">
+        <v>36941</v>
       </c>
       <c r="J194" s="7" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>192</v>
       </c>
@@ -8963,20 +8963,20 @@
       <c r="F195" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G195" s="40" t="s">
-        <v>331</v>
+      <c r="G195" s="34" t="s">
+        <v>333</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>12</v>
       </c>
       <c r="I195" s="8">
-        <v>39373</v>
+        <v>41078</v>
       </c>
       <c r="J195" s="7" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>193</v>
       </c>
@@ -8987,28 +8987,28 @@
         <v>328</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="G196" s="33" t="s">
-        <v>353</v>
+        <v>667</v>
+      </c>
+      <c r="G196" s="34" t="s">
+        <v>335</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I196" s="8">
-        <v>39975</v>
+        <v>41078</v>
       </c>
       <c r="J196" s="7" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>194</v>
       </c>
@@ -9025,22 +9025,22 @@
         <v>10</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G197" s="34" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="I197" s="8">
-        <v>41078</v>
+        <v>41816</v>
       </c>
       <c r="J197" s="7" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>195</v>
       </c>
@@ -9057,22 +9057,22 @@
         <v>10</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G198" s="34" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I198" s="8">
-        <v>41078</v>
+        <v>41824</v>
       </c>
       <c r="J198" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>196</v>
       </c>
@@ -9089,22 +9089,22 @@
         <v>10</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G199" s="34" t="s">
-        <v>337</v>
-      </c>
-      <c r="H199" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="H199" s="27" t="s">
         <v>53</v>
       </c>
       <c r="I199" s="8">
-        <v>41816</v>
+        <v>43269</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="200" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>197</v>
       </c>
@@ -9121,22 +9121,22 @@
         <v>10</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G200" s="34" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I200" s="8">
-        <v>41824</v>
+        <v>44417</v>
       </c>
       <c r="J200" s="7" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="201" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>198</v>
       </c>
@@ -9147,28 +9147,28 @@
         <v>328</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G201" s="27" t="s">
-        <v>355</v>
+      <c r="G201" s="34" t="s">
+        <v>345</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I201" s="8">
-        <v>42537</v>
+        <v>44418</v>
       </c>
       <c r="J201" s="7" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>199</v>
       </c>
@@ -9179,28 +9179,28 @@
         <v>328</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G202" s="27" t="s">
-        <v>357</v>
+      <c r="G202" s="34" t="s">
+        <v>347</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I202" s="8">
-        <v>42537</v>
+        <v>44419</v>
       </c>
       <c r="J202" s="7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>200</v>
       </c>
@@ -9220,19 +9220,19 @@
         <v>667</v>
       </c>
       <c r="G203" s="34" t="s">
-        <v>341</v>
-      </c>
-      <c r="H203" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="I203" s="8">
-        <v>43269</v>
+        <v>349</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I203" s="17">
+        <v>44762</v>
       </c>
       <c r="J203" s="7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>201</v>
       </c>
@@ -9252,19 +9252,19 @@
         <v>667</v>
       </c>
       <c r="G204" s="27" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I204" s="8">
-        <v>44075</v>
+      <c r="I204" s="16">
+        <v>37795</v>
       </c>
       <c r="J204" s="7" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>202</v>
       </c>
@@ -9281,22 +9281,22 @@
         <v>40</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="G205" s="27" t="s">
-        <v>361</v>
+        <v>668</v>
+      </c>
+      <c r="G205" s="33" t="s">
+        <v>353</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I205" s="8">
-        <v>44075</v>
-      </c>
-      <c r="J205" s="9" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39975</v>
+      </c>
+      <c r="J205" s="7" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>203</v>
       </c>
@@ -9316,19 +9316,19 @@
         <v>667</v>
       </c>
       <c r="G206" s="27" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I206" s="8">
-        <v>44075</v>
+        <v>42537</v>
       </c>
       <c r="J206" s="7" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="207" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>204</v>
       </c>
@@ -9339,28 +9339,28 @@
         <v>328</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G207" s="34" t="s">
-        <v>343</v>
+      <c r="G207" s="27" t="s">
+        <v>357</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I207" s="8">
-        <v>44417</v>
+        <v>42537</v>
       </c>
       <c r="J207" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>205</v>
       </c>
@@ -9371,28 +9371,28 @@
         <v>328</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G208" s="34" t="s">
-        <v>345</v>
+      <c r="G208" s="27" t="s">
+        <v>359</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I208" s="8">
-        <v>44418</v>
+        <v>44075</v>
       </c>
       <c r="J208" s="7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="209" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>206</v>
       </c>
@@ -9403,28 +9403,28 @@
         <v>328</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G209" s="34" t="s">
-        <v>347</v>
+      <c r="G209" s="27" t="s">
+        <v>361</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I209" s="8">
-        <v>44419</v>
-      </c>
-      <c r="J209" s="7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44075</v>
+      </c>
+      <c r="J209" s="9" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>207</v>
       </c>
@@ -9435,28 +9435,28 @@
         <v>328</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G210" s="34" t="s">
-        <v>349</v>
+      <c r="G210" s="27" t="s">
+        <v>363</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I210" s="17">
-        <v>44762</v>
+      <c r="I210" s="8">
+        <v>44075</v>
       </c>
       <c r="J210" s="7" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>208</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>209</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>210</v>
       </c>
@@ -9552,7 +9552,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>211</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>212</v>
       </c>
@@ -9616,7 +9616,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>213</v>
       </c>
@@ -9648,7 +9648,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>214</v>
       </c>
@@ -9680,7 +9680,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>215</v>
       </c>
@@ -9712,7 +9712,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>216</v>
       </c>
@@ -9744,7 +9744,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>217</v>
       </c>
@@ -9761,22 +9761,22 @@
         <v>40</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="G220" s="27" t="s">
-        <v>387</v>
+        <v>667</v>
+      </c>
+      <c r="G220" s="33" t="s">
+        <v>384</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="I220" s="8">
-        <v>39246</v>
-      </c>
-      <c r="J220" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I220" s="15">
+        <v>41445</v>
+      </c>
+      <c r="J220" s="7" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>218</v>
       </c>
@@ -9793,22 +9793,22 @@
         <v>40</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="G221" s="33" t="s">
-        <v>384</v>
+        <v>668</v>
+      </c>
+      <c r="G221" s="27" t="s">
+        <v>387</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="I221" s="15">
-        <v>41445</v>
-      </c>
-      <c r="J221" s="7" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="222" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I221" s="8">
+        <v>39246</v>
+      </c>
+      <c r="J221" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>219</v>
       </c>
@@ -9840,7 +9840,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>220</v>
       </c>
@@ -9872,7 +9872,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>221</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>222</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>223</v>
       </c>
@@ -9968,7 +9968,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>224</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>225</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>226</v>
       </c>
@@ -10051,20 +10051,20 @@
       <c r="F229" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G229" s="28" t="s">
-        <v>407</v>
+      <c r="G229" s="38" t="s">
+        <v>405</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>12</v>
       </c>
       <c r="I229" s="8">
-        <v>36535</v>
+        <v>39373</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>227</v>
       </c>
@@ -10083,20 +10083,20 @@
       <c r="F230" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G230" s="38" t="s">
-        <v>405</v>
+      <c r="G230" s="28" t="s">
+        <v>407</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>12</v>
       </c>
       <c r="I230" s="8">
-        <v>39373</v>
+        <v>36535</v>
       </c>
       <c r="J230" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="231" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>228</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>229</v>
       </c>
@@ -10160,7 +10160,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>230</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>231</v>
       </c>
@@ -10224,7 +10224,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>232</v>
       </c>
@@ -10256,7 +10256,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>233</v>
       </c>
@@ -10288,7 +10288,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>234</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>235</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>236</v>
       </c>
@@ -10363,28 +10363,28 @@
         <v>425</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F239" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G239" s="27" t="s">
-        <v>436</v>
+      <c r="G239" s="28" t="s">
+        <v>426</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I239" s="8">
-        <v>39246</v>
+        <v>41078</v>
       </c>
       <c r="J239" s="2" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>237</v>
       </c>
@@ -10403,20 +10403,20 @@
       <c r="F240" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G240" s="28" t="s">
-        <v>426</v>
+      <c r="G240" s="38" t="s">
+        <v>432</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="I240" s="8">
-        <v>41078</v>
+        <v>41446</v>
       </c>
       <c r="J240" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>238</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>239</v>
       </c>
@@ -10465,22 +10465,22 @@
         <v>10</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G242" s="28" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I242" s="8">
-        <v>41447</v>
+        <v>41445</v>
       </c>
       <c r="J242" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>240</v>
       </c>
@@ -10497,22 +10497,22 @@
         <v>10</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G243" s="28" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I243" s="8">
-        <v>41445</v>
+        <v>41447</v>
       </c>
       <c r="J243" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>241</v>
       </c>
@@ -10523,28 +10523,28 @@
         <v>425</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F244" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G244" s="38" t="s">
-        <v>432</v>
+      <c r="G244" s="27" t="s">
+        <v>436</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I244" s="8">
-        <v>41446</v>
+        <v>39246</v>
       </c>
       <c r="J244" s="2" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>242</v>
       </c>
@@ -10576,7 +10576,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>243</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="247" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>244</v>
       </c>
@@ -10640,7 +10640,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="248" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>245</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="249" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>246</v>
       </c>
@@ -10704,7 +10704,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="250" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>247</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>248</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>249</v>
       </c>
@@ -10800,7 +10800,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>250</v>
       </c>
@@ -10832,7 +10832,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>251</v>
       </c>
@@ -10864,7 +10864,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="255" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>252</v>
       </c>
@@ -10896,7 +10896,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>253</v>
       </c>
@@ -10928,7 +10928,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>254</v>
       </c>
@@ -10960,7 +10960,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>255</v>
       </c>
@@ -10992,7 +10992,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>256</v>
       </c>
@@ -11020,7 +11020,7 @@
       <c r="I259" s="8"/>
       <c r="J259" s="37"/>
     </row>
-    <row r="260" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>257</v>
       </c>
@@ -11052,7 +11052,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>258</v>
       </c>
@@ -11084,7 +11084,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>259</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>260</v>
       </c>
@@ -11148,7 +11148,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>261</v>
       </c>
@@ -11180,7 +11180,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>262</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="266" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>263</v>
       </c>
@@ -11244,7 +11244,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>264</v>
       </c>
@@ -11276,7 +11276,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>265</v>
       </c>
@@ -11308,7 +11308,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>266</v>
       </c>
@@ -11340,7 +11340,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>267</v>
       </c>
@@ -11372,7 +11372,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>268</v>
       </c>
@@ -11383,28 +11383,28 @@
         <v>464</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G271" s="34" t="s">
-        <v>497</v>
+      <c r="G271" s="28" t="s">
+        <v>485</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I271" s="8">
-        <v>42537</v>
+      <c r="I271" s="17">
+        <v>43269</v>
       </c>
       <c r="J271" s="7" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="272" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>269</v>
       </c>
@@ -11424,19 +11424,19 @@
         <v>667</v>
       </c>
       <c r="G272" s="28" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I272" s="17">
-        <v>43269</v>
+        <v>43633</v>
       </c>
       <c r="J272" s="7" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>270</v>
       </c>
@@ -11456,19 +11456,19 @@
         <v>667</v>
       </c>
       <c r="G273" s="28" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I273" s="17">
-        <v>43633</v>
+        <v>43634</v>
       </c>
       <c r="J273" s="7" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="274" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>271</v>
       </c>
@@ -11488,19 +11488,19 @@
         <v>667</v>
       </c>
       <c r="G274" s="28" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I274" s="17">
-        <v>43634</v>
+        <v>44417</v>
       </c>
       <c r="J274" s="7" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="275" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>272</v>
       </c>
@@ -11520,19 +11520,19 @@
         <v>667</v>
       </c>
       <c r="G275" s="28" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I275" s="17">
-        <v>44417</v>
+        <v>45096</v>
       </c>
       <c r="J275" s="7" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="276" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>273</v>
       </c>
@@ -11552,19 +11552,19 @@
         <v>667</v>
       </c>
       <c r="G276" s="28" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I276" s="17">
-        <v>45096</v>
+      <c r="I276" s="8">
+        <v>46189</v>
       </c>
       <c r="J276" s="7" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="277" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>274</v>
       </c>
@@ -11581,22 +11581,22 @@
         <v>40</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G277" s="34" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I277" s="8">
-        <v>45462</v>
+        <v>42537</v>
       </c>
       <c r="J277" s="7" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="278" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>275</v>
       </c>
@@ -11607,28 +11607,28 @@
         <v>464</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="G278" s="28" t="s">
-        <v>495</v>
+        <v>668</v>
+      </c>
+      <c r="G278" s="34" t="s">
+        <v>499</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I278" s="8">
-        <v>46189</v>
+        <v>45462</v>
       </c>
       <c r="J278" s="7" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="279" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>276</v>
       </c>
@@ -11660,7 +11660,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="280" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>277</v>
       </c>
@@ -11677,22 +11677,22 @@
         <v>40</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="G280" s="27" t="s">
-        <v>510</v>
+        <v>668</v>
+      </c>
+      <c r="G280" s="33" t="s">
+        <v>504</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I280" s="8">
-        <v>43269</v>
+        <v>44075</v>
       </c>
       <c r="J280" s="7" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="281" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>278</v>
       </c>
@@ -11709,22 +11709,22 @@
         <v>40</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="G281" s="33" t="s">
-        <v>504</v>
+        <v>667</v>
+      </c>
+      <c r="G281" s="28" t="s">
+        <v>506</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I281" s="8">
-        <v>44075</v>
+        <v>44417</v>
       </c>
       <c r="J281" s="7" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="282" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>279</v>
       </c>
@@ -11743,20 +11743,20 @@
       <c r="F282" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G282" s="28" t="s">
-        <v>506</v>
+      <c r="G282" s="27" t="s">
+        <v>510</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I282" s="8">
-        <v>44417</v>
+        <v>43269</v>
       </c>
       <c r="J282" s="7" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="283" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>280</v>
       </c>
@@ -11772,23 +11772,23 @@
       <c r="E283" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F283" s="11" t="s">
-        <v>668</v>
+      <c r="F283" s="2" t="s">
+        <v>667</v>
       </c>
       <c r="G283" s="27" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I283" s="8">
-        <v>45462</v>
+        <v>45231</v>
       </c>
       <c r="J283" s="7" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>281</v>
       </c>
@@ -11804,11 +11804,11 @@
       <c r="E284" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F284" s="2" t="s">
+      <c r="F284" s="11" t="s">
         <v>668</v>
       </c>
-      <c r="G284" s="28" t="s">
-        <v>514</v>
+      <c r="G284" s="27" t="s">
+        <v>512</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>53</v>
@@ -11817,10 +11817,10 @@
         <v>45462</v>
       </c>
       <c r="J284" s="7" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="285" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>282</v>
       </c>
@@ -11837,22 +11837,22 @@
         <v>40</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="G285" s="27" t="s">
-        <v>508</v>
+        <v>668</v>
+      </c>
+      <c r="G285" s="28" t="s">
+        <v>514</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I285" s="8">
-        <v>45231</v>
+        <v>45462</v>
       </c>
       <c r="J285" s="7" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="286" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>283</v>
       </c>
@@ -11884,7 +11884,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="287" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>284</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="288" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>285</v>
       </c>
@@ -11948,7 +11948,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="289" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
         <v>286</v>
       </c>
@@ -11965,22 +11965,22 @@
         <v>10</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="G289" s="34" t="s">
-        <v>531</v>
+        <v>667</v>
+      </c>
+      <c r="G289" s="40" t="s">
+        <v>523</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>12</v>
       </c>
       <c r="I289" s="17">
-        <v>39377</v>
+        <v>33204</v>
       </c>
       <c r="J289" s="7" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="290" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>287</v>
       </c>
@@ -11991,28 +11991,28 @@
         <v>522</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="G290" s="27" t="s">
-        <v>561</v>
+        <v>667</v>
+      </c>
+      <c r="G290" s="34" t="s">
+        <v>525</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I290" s="17">
-        <v>43633</v>
+        <v>36539</v>
       </c>
       <c r="J290" s="7" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="291" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
         <v>288</v>
       </c>
@@ -12023,28 +12023,28 @@
         <v>522</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="G291" s="27" t="s">
-        <v>563</v>
+        <v>667</v>
+      </c>
+      <c r="G291" s="34" t="s">
+        <v>527</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I291" s="17">
-        <v>43633</v>
+        <v>38980</v>
       </c>
       <c r="J291" s="7" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="292" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>289</v>
       </c>
@@ -12055,28 +12055,28 @@
         <v>522</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="G292" s="27" t="s">
-        <v>569</v>
+        <v>667</v>
+      </c>
+      <c r="G292" s="34" t="s">
+        <v>529</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I292" s="17">
-        <v>44760</v>
+        <v>39374</v>
       </c>
       <c r="J292" s="7" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="293" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
         <v>290</v>
       </c>
@@ -12087,28 +12087,28 @@
         <v>522</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>668</v>
       </c>
       <c r="G293" s="34" t="s">
-        <v>573</v>
+        <v>531</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="I293" s="17">
-        <v>46218</v>
-      </c>
-      <c r="J293" s="12" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="294" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39377</v>
+      </c>
+      <c r="J293" s="7" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>291</v>
       </c>
@@ -12127,20 +12127,20 @@
       <c r="F294" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G294" s="40" t="s">
-        <v>523</v>
+      <c r="G294" s="34" t="s">
+        <v>533</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I294" s="17">
-        <v>33204</v>
+        <v>53</v>
+      </c>
+      <c r="I294" s="8">
+        <v>41078</v>
       </c>
       <c r="J294" s="7" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
         <v>292</v>
       </c>
@@ -12160,19 +12160,19 @@
         <v>667</v>
       </c>
       <c r="G295" s="34" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="I295" s="17">
-        <v>36539</v>
+        <v>41078</v>
       </c>
       <c r="J295" s="7" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="296" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>293</v>
       </c>
@@ -12192,19 +12192,19 @@
         <v>667</v>
       </c>
       <c r="G296" s="34" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="I296" s="17">
-        <v>38980</v>
+        <v>42173</v>
       </c>
       <c r="J296" s="7" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="297" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
         <v>294</v>
       </c>
@@ -12215,28 +12215,28 @@
         <v>522</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G297" s="27" t="s">
-        <v>557</v>
+      <c r="G297" s="34" t="s">
+        <v>539</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I297" s="15">
-        <v>39237</v>
+      <c r="I297" s="17">
+        <v>42537</v>
       </c>
       <c r="J297" s="7" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="298" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>295</v>
       </c>
@@ -12256,19 +12256,19 @@
         <v>667</v>
       </c>
       <c r="G298" s="34" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="I298" s="17">
-        <v>39374</v>
+        <v>42538</v>
       </c>
       <c r="J298" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="299" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
         <v>296</v>
       </c>
@@ -12279,28 +12279,28 @@
         <v>522</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G299" s="33" t="s">
-        <v>559</v>
+      <c r="G299" s="34" t="s">
+        <v>543</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I299" s="15">
-        <v>40707</v>
+      <c r="I299" s="17">
+        <v>43269</v>
       </c>
       <c r="J299" s="7" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="300" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>297</v>
       </c>
@@ -12320,19 +12320,19 @@
         <v>667</v>
       </c>
       <c r="G300" s="34" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I300" s="8">
-        <v>41078</v>
+      <c r="I300" s="17">
+        <v>43270</v>
       </c>
       <c r="J300" s="7" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="301" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
         <v>298</v>
       </c>
@@ -12352,19 +12352,19 @@
         <v>667</v>
       </c>
       <c r="G301" s="34" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I301" s="17">
-        <v>41078</v>
+        <v>44417</v>
       </c>
       <c r="J301" s="7" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="302" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>299</v>
       </c>
@@ -12384,19 +12384,19 @@
         <v>667</v>
       </c>
       <c r="G302" s="34" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I302" s="17">
-        <v>42173</v>
+        <v>44762</v>
       </c>
       <c r="J302" s="7" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
         <v>300</v>
       </c>
@@ -12416,19 +12416,19 @@
         <v>667</v>
       </c>
       <c r="G303" s="34" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I303" s="17">
-        <v>42537</v>
+        <v>45096</v>
       </c>
       <c r="J303" s="7" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="304" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>301</v>
       </c>
@@ -12448,19 +12448,19 @@
         <v>667</v>
       </c>
       <c r="G304" s="34" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I304" s="17">
-        <v>42538</v>
+        <v>45097</v>
       </c>
       <c r="J304" s="7" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="305" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
         <v>302</v>
       </c>
@@ -12480,19 +12480,19 @@
         <v>667</v>
       </c>
       <c r="G305" s="34" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I305" s="17">
-        <v>43269</v>
+        <v>45824</v>
       </c>
       <c r="J305" s="7" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>303</v>
       </c>
@@ -12503,28 +12503,28 @@
         <v>522</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G306" s="34" t="s">
-        <v>545</v>
+      <c r="G306" s="27" t="s">
+        <v>557</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I306" s="17">
-        <v>43270</v>
+      <c r="I306" s="15">
+        <v>39237</v>
       </c>
       <c r="J306" s="7" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="307" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
         <v>304</v>
       </c>
@@ -12543,20 +12543,20 @@
       <c r="F307" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G307" s="27" t="s">
-        <v>565</v>
+      <c r="G307" s="33" t="s">
+        <v>559</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I307" s="21">
-        <v>43633</v>
+      <c r="I307" s="15">
+        <v>40707</v>
       </c>
       <c r="J307" s="7" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="308" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>305</v>
       </c>
@@ -12567,28 +12567,28 @@
         <v>522</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="G308" s="34" t="s">
-        <v>547</v>
+        <v>668</v>
+      </c>
+      <c r="G308" s="27" t="s">
+        <v>561</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I308" s="17">
-        <v>44417</v>
+        <v>43633</v>
       </c>
       <c r="J308" s="7" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="309" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>306</v>
       </c>
@@ -12599,28 +12599,28 @@
         <v>522</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="G309" s="34" t="s">
-        <v>549</v>
+        <v>668</v>
+      </c>
+      <c r="G309" s="27" t="s">
+        <v>563</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I309" s="17">
-        <v>44762</v>
+        <v>43633</v>
       </c>
       <c r="J309" s="7" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="310" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>307</v>
       </c>
@@ -12640,19 +12640,19 @@
         <v>667</v>
       </c>
       <c r="G310" s="27" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I310" s="15">
-        <v>44760</v>
+      <c r="I310" s="21">
+        <v>43633</v>
       </c>
       <c r="J310" s="7" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="311" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>308</v>
       </c>
@@ -12672,19 +12672,19 @@
         <v>667</v>
       </c>
       <c r="G311" s="27" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I311" s="17">
+      <c r="I311" s="15">
         <v>44760</v>
       </c>
       <c r="J311" s="7" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="312" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>309</v>
       </c>
@@ -12695,28 +12695,28 @@
         <v>522</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="G312" s="34" t="s">
-        <v>551</v>
+        <v>668</v>
+      </c>
+      <c r="G312" s="27" t="s">
+        <v>569</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I312" s="17">
-        <v>45096</v>
+        <v>44760</v>
       </c>
       <c r="J312" s="7" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="313" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>310</v>
       </c>
@@ -12727,28 +12727,28 @@
         <v>522</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F313" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="G313" s="34" t="s">
-        <v>553</v>
+      <c r="G313" s="27" t="s">
+        <v>571</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I313" s="17">
-        <v>45097</v>
+        <v>44760</v>
       </c>
       <c r="J313" s="7" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="314" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>311</v>
       </c>
@@ -12759,28 +12759,28 @@
         <v>522</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G314" s="34" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>53</v>
       </c>
       <c r="I314" s="17">
-        <v>45824</v>
-      </c>
-      <c r="J314" s="7" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="315" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46218</v>
+      </c>
+      <c r="J314" s="12" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="3">
         <v>312</v>
       </c>
@@ -12812,7 +12812,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="316" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>313</v>
       </c>
@@ -12844,7 +12844,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>314</v>
       </c>
@@ -12876,7 +12876,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="318" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>315</v>
       </c>
@@ -12908,7 +12908,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="319" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>316</v>
       </c>
@@ -12940,7 +12940,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="320" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>317</v>
       </c>
@@ -12992,28 +12992,28 @@
     <hyperlink ref="J191" r:id="rId11" xr:uid="{F8DAD546-FB0A-4E39-BA6B-5B657CA3248F}"/>
     <hyperlink ref="J189" r:id="rId12" xr:uid="{74D025AC-810F-4FB6-97A8-B4EA761B3BD3}"/>
     <hyperlink ref="J188" r:id="rId13" xr:uid="{B9526886-B36B-4874-AC88-887A0D0371FE}"/>
-    <hyperlink ref="J186" r:id="rId14" xr:uid="{E17809DC-9633-4717-9F96-1AAD3D6D0559}"/>
+    <hyperlink ref="J187" r:id="rId14" xr:uid="{E17809DC-9633-4717-9F96-1AAD3D6D0559}"/>
     <hyperlink ref="J185" r:id="rId15" xr:uid="{F6D4878E-3EDA-498A-8DFB-9B35F0B1C313}"/>
-    <hyperlink ref="J187" r:id="rId16" xr:uid="{E0056A04-BC1D-490F-89ED-E90871AB5B33}"/>
+    <hyperlink ref="J186" r:id="rId16" xr:uid="{E0056A04-BC1D-490F-89ED-E90871AB5B33}"/>
     <hyperlink ref="J51" r:id="rId17" xr:uid="{AF01CBB9-7542-48A4-82E3-A5DB0C391183}"/>
-    <hyperlink ref="J49" r:id="rId18" xr:uid="{4AA06068-7E81-4F89-BD4F-8C0AB3B69AA0}"/>
-    <hyperlink ref="J30" r:id="rId19" xr:uid="{2A560989-E0F9-4C2B-A000-2A0270B5A34D}"/>
-    <hyperlink ref="J43" r:id="rId20" display="mailto:perumal_co2@mail.sjctni.edu" xr:uid="{18F83F44-2521-4B03-8BB9-A7B7E34E445B}"/>
-    <hyperlink ref="J42" r:id="rId21" display="mailto:mariyaselvia_co2@mail.sjctni.edu" xr:uid="{B5830726-AF10-4E47-8F31-6ED5D51732BF}"/>
-    <hyperlink ref="J41" r:id="rId22" display="mailto:berkmansj_co2@mail.sjctni.edu" xr:uid="{AEE9D962-3581-4B2D-8189-DDAA2B489E49}"/>
-    <hyperlink ref="J40" r:id="rId23" display="mailto:ignatiusa_co2@mail.sjctni.edu" xr:uid="{E69F8DEE-7D57-449B-81E6-F406EE82AE74}"/>
-    <hyperlink ref="J39" r:id="rId24" display="mailto:soundarya_co2@mail.sjctni.edu" xr:uid="{475EABB3-97D5-4FC7-8E6F-87690EF72852}"/>
-    <hyperlink ref="J38" r:id="rId25" display="mailto:nalini_co2@mail.sjctni.edu" xr:uid="{C3F16A76-E5BB-44A3-B813-4005C7252083}"/>
-    <hyperlink ref="J34" r:id="rId26" display="mailto:jerome_co2@mail.sjctni.edu" xr:uid="{8491C2EA-1709-4106-B3B7-7BEC6458806F}"/>
-    <hyperlink ref="J28" r:id="rId27" display="mailto:juliasceasar_co1@mail.sjctni.edu" xr:uid="{37F3A527-0A2E-47AB-A65C-EA33AF5DF6FE}"/>
-    <hyperlink ref="J31" r:id="rId28" display="mailto:antonyjesuraja_co1@mail.sjctni.edu" xr:uid="{0F7E78F0-94A7-49DC-9B6D-CAABEB5C4DAF}"/>
-    <hyperlink ref="J44" r:id="rId29" xr:uid="{303E383B-4C65-4012-B21F-54F0690CDD25}"/>
-    <hyperlink ref="J45" r:id="rId30" display="mailto:vinothkumar_co1@mail.sjctni.edu" xr:uid="{6E851293-432A-4E54-9331-02C3B3E8FBED}"/>
-    <hyperlink ref="J37" r:id="rId31" display="mailto:georgia_co1@mail.sjctni.edu" xr:uid="{6B69BF9D-0D7E-4861-A634-8C4DF6A9A716}"/>
-    <hyperlink ref="J36" r:id="rId32" display="mailto:sahayarajalexander_co1@mail.sjctni.edu" xr:uid="{7A4DBC64-FFEC-43AC-9239-56F3961ACF18}"/>
-    <hyperlink ref="J35" r:id="rId33" display="mailto:aruldass_co1@mail.sjctni.edu" xr:uid="{077E5E5A-90D8-437D-BE61-644370F07A59}"/>
-    <hyperlink ref="J33" r:id="rId34" display="mailto:arockiarajasekar_co1@mail.sjctni.edu" xr:uid="{0ACEBB58-D5BD-43B5-B308-1BD9E17CBEBA}"/>
-    <hyperlink ref="J32" r:id="rId35" display="mailto:francisvijayakumar_co1@mail.sjctni.edu" xr:uid="{8ABB71DA-10D9-4116-B377-F9EF7DF95FFC}"/>
+    <hyperlink ref="J50" r:id="rId18" xr:uid="{4AA06068-7E81-4F89-BD4F-8C0AB3B69AA0}"/>
+    <hyperlink ref="J38" r:id="rId19" xr:uid="{2A560989-E0F9-4C2B-A000-2A0270B5A34D}"/>
+    <hyperlink ref="J45" r:id="rId20" display="mailto:perumal_co2@mail.sjctni.edu" xr:uid="{18F83F44-2521-4B03-8BB9-A7B7E34E445B}"/>
+    <hyperlink ref="J44" r:id="rId21" display="mailto:mariyaselvia_co2@mail.sjctni.edu" xr:uid="{B5830726-AF10-4E47-8F31-6ED5D51732BF}"/>
+    <hyperlink ref="J43" r:id="rId22" display="mailto:berkmansj_co2@mail.sjctni.edu" xr:uid="{AEE9D962-3581-4B2D-8189-DDAA2B489E49}"/>
+    <hyperlink ref="J42" r:id="rId23" display="mailto:ignatiusa_co2@mail.sjctni.edu" xr:uid="{E69F8DEE-7D57-449B-81E6-F406EE82AE74}"/>
+    <hyperlink ref="J41" r:id="rId24" display="mailto:soundarya_co2@mail.sjctni.edu" xr:uid="{475EABB3-97D5-4FC7-8E6F-87690EF72852}"/>
+    <hyperlink ref="J40" r:id="rId25" display="mailto:nalini_co2@mail.sjctni.edu" xr:uid="{C3F16A76-E5BB-44A3-B813-4005C7252083}"/>
+    <hyperlink ref="J39" r:id="rId26" display="mailto:jerome_co2@mail.sjctni.edu" xr:uid="{8491C2EA-1709-4106-B3B7-7BEC6458806F}"/>
+    <hyperlink ref="J30" r:id="rId27" display="mailto:juliasceasar_co1@mail.sjctni.edu" xr:uid="{37F3A527-0A2E-47AB-A65C-EA33AF5DF6FE}"/>
+    <hyperlink ref="J28" r:id="rId28" display="mailto:antonyjesuraja_co1@mail.sjctni.edu" xr:uid="{0F7E78F0-94A7-49DC-9B6D-CAABEB5C4DAF}"/>
+    <hyperlink ref="J35" r:id="rId29" xr:uid="{303E383B-4C65-4012-B21F-54F0690CDD25}"/>
+    <hyperlink ref="J36" r:id="rId30" display="mailto:vinothkumar_co1@mail.sjctni.edu" xr:uid="{6E851293-432A-4E54-9331-02C3B3E8FBED}"/>
+    <hyperlink ref="J34" r:id="rId31" display="mailto:georgia_co1@mail.sjctni.edu" xr:uid="{6B69BF9D-0D7E-4861-A634-8C4DF6A9A716}"/>
+    <hyperlink ref="J33" r:id="rId32" display="mailto:sahayarajalexander_co1@mail.sjctni.edu" xr:uid="{7A4DBC64-FFEC-43AC-9239-56F3961ACF18}"/>
+    <hyperlink ref="J32" r:id="rId33" display="mailto:aruldass_co1@mail.sjctni.edu" xr:uid="{077E5E5A-90D8-437D-BE61-644370F07A59}"/>
+    <hyperlink ref="J31" r:id="rId34" display="mailto:arockiarajasekar_co1@mail.sjctni.edu" xr:uid="{0ACEBB58-D5BD-43B5-B308-1BD9E17CBEBA}"/>
+    <hyperlink ref="J29" r:id="rId35" display="mailto:francisvijayakumar_co1@mail.sjctni.edu" xr:uid="{8ABB71DA-10D9-4116-B377-F9EF7DF95FFC}"/>
     <hyperlink ref="J27" r:id="rId36" display="mailto:bastinjerome_co1@mail.sjctni.edu" xr:uid="{0E901B83-165D-43E4-A282-592B0763858B}"/>
     <hyperlink ref="J26" r:id="rId37" display="mailto:mariaantony_co1@mail.sjctni.edu" xr:uid="{49E86B32-EAFD-41CF-A61D-C6C60C298688}"/>
     <hyperlink ref="J25" r:id="rId38" display="mailto:john_co1@mail.sjctni.edu" xr:uid="{45B87E79-36B3-45EB-9A67-654728D11D6B}"/>
@@ -13025,52 +13025,52 @@
     <hyperlink ref="J54" r:id="rId44" xr:uid="{8F054987-4B3F-4213-8977-DFF27EE8B2B2}"/>
     <hyperlink ref="J53" r:id="rId45" xr:uid="{C0B69169-4E7D-4F6E-9590-8D6CFF68F9F2}"/>
     <hyperlink ref="J52" r:id="rId46" xr:uid="{17096A0C-E7BD-452F-A7BD-E9D6AC6B070D}"/>
-    <hyperlink ref="J50" r:id="rId47" xr:uid="{F6BC87AD-1A0D-4EED-B2FE-B23AF5D55A46}"/>
+    <hyperlink ref="J49" r:id="rId47" xr:uid="{F6BC87AD-1A0D-4EED-B2FE-B23AF5D55A46}"/>
     <hyperlink ref="J249" r:id="rId48" display="mailto:ramesh_pe1@mail.sjctni.edu" xr:uid="{466F5511-153C-40FE-AE87-CD2A60F2AF02}"/>
     <hyperlink ref="J248" r:id="rId49" display="mailto:sriram_pe1@mail.sjctni.edu" xr:uid="{AFCD3BFA-F7EF-4E27-BCFA-BF9C28EBC90C}"/>
     <hyperlink ref="J247" r:id="rId50" xr:uid="{3D6A4348-CBBE-4BB7-A8BE-DAF1B1F3B113}"/>
-    <hyperlink ref="J293" r:id="rId51" xr:uid="{A88778FF-CC52-4A9B-AC10-FBF8F003482B}"/>
-    <hyperlink ref="J311" r:id="rId52" display="mailto:rexrosario_ph2@mail.sjctni.edu" xr:uid="{02E9D1FC-4AA3-4692-896E-A3BDF0BE05B5}"/>
-    <hyperlink ref="J292" r:id="rId53" display="mailto:genifersilvena_ph2@mail.sjctni.edu" xr:uid="{2885B73C-64D3-4DD2-94F9-0C6BD170E997}"/>
-    <hyperlink ref="J310" r:id="rId54" display="mailto:augustin_ph2@mail.sjctni.edu" xr:uid="{8BBE3203-CF46-49C7-924B-76E7C3F6BA60}"/>
-    <hyperlink ref="J307" r:id="rId55" xr:uid="{48B90131-A1FC-4664-AE28-0E36C27F27F2}"/>
-    <hyperlink ref="J291" r:id="rId56" display="mailto:marydayana_ph2@mail.sjctni.edu" xr:uid="{1ADA392F-1DB7-45BC-AF35-28E902D09B00}"/>
-    <hyperlink ref="J290" r:id="rId57" display="mailto:sinthiya_ph2@mail.sjctni.edu" xr:uid="{CC18D803-8EF1-4776-9026-D8D681F09D2A}"/>
-    <hyperlink ref="J299" r:id="rId58" display="mailto:adalarasu_ph2@mail.sjctni.edu" xr:uid="{4924706F-6BB7-45FB-81EA-D14242C654E9}"/>
-    <hyperlink ref="J297" r:id="rId59" display="mailto:lourduraj_ph2@mail.sjctni.edu" xr:uid="{2ADF6A09-0EAF-4882-8858-F0627CE6955A}"/>
-    <hyperlink ref="J314" r:id="rId60" display="mailto:alexandar_ph1@mail.sjctni.edu" xr:uid="{A16B5392-E809-43DA-A116-1B32FB1294AE}"/>
-    <hyperlink ref="J313" r:id="rId61" display="mailto:prathaps_ph1@mail.sjctni.edu" xr:uid="{DC7F01D7-8D92-4141-BB19-A1A1FF5EFC9E}"/>
-    <hyperlink ref="J312" r:id="rId62" display="mailto:thomasr_ph1@mail.sjctni.edu" xr:uid="{A10B6E28-32A4-4B1E-9A6B-A7EA32A49340}"/>
-    <hyperlink ref="J309" r:id="rId63" display="mailto:joyprabu_ph2@mail.sjctni.edu" xr:uid="{74E710CF-3684-4FB6-B014-BE13EEC77422}"/>
-    <hyperlink ref="J308" r:id="rId64" display="mailto:samuel_ph1@mail.sjctni.edu" xr:uid="{DA8912AE-022B-46D2-8916-BCE1972E9492}"/>
-    <hyperlink ref="J306" r:id="rId65" display="mailto:antonyraj_ph1@mail.sjctni.edu" xr:uid="{27DB355E-49F2-410A-9F9E-BDDF58198A6B}"/>
-    <hyperlink ref="J305" r:id="rId66" display="mailto:anbarasu_ph1@mail.sjctni.edu" xr:uid="{9265CE46-B1F2-4697-B87D-BBBE9A7982A1}"/>
-    <hyperlink ref="J304" r:id="rId67" display="mailto:dinakaran_ph1@mail.sjctni.edu" xr:uid="{EB33C7C6-5D23-44C2-A8DE-B55D9374489A}"/>
-    <hyperlink ref="J303" r:id="rId68" display="mailto:jeraldvijay_ph1@mail.sjctni.edu" xr:uid="{561368F0-A622-4BAB-B9A5-3CA124A1A1C5}"/>
-    <hyperlink ref="J302" r:id="rId69" display="mailto:antonyarockiaraj_ph1@mail.sjctni.edu" xr:uid="{415FE73F-5F8A-46B0-A760-89EADF8DA138}"/>
-    <hyperlink ref="J301" r:id="rId70" display="mailto:clementlourduraj_ph1@mail.sjctni.edu" xr:uid="{AC1776E9-055E-488A-A0A9-8E709B50DB1F}"/>
-    <hyperlink ref="J300" r:id="rId71" display="mailto:armstrongarasu_ph1@mail.sjctni.edu" xr:uid="{419EED2D-86CF-4C0A-9A33-EB50E111DE91}"/>
-    <hyperlink ref="J289" r:id="rId72" display="mailto:maggiedayana_ph1@mail.sjctni.edu" xr:uid="{132719D8-060D-402D-9D4D-6C6DB9605CFE}"/>
-    <hyperlink ref="J298" r:id="rId73" display="mailto:christuraj_ph1@mail.sjctni.edu" xr:uid="{35E2E9CB-0FF5-43A8-8A2B-AD81A0635AC7}"/>
-    <hyperlink ref="J296" r:id="rId74" display="mailto:charles_ph1@mail.sjctni.edu" xr:uid="{8594491B-D151-4F0D-A859-40B74EC40715}"/>
-    <hyperlink ref="J295" r:id="rId75" display="mailto:kanickairaj_ph1@mail.sjctni.edu" xr:uid="{6DEA60E9-E59A-430A-B209-6506C688C734}"/>
-    <hyperlink ref="J294" r:id="rId76" display="mailto:johnson_ph1@mail.sjctni.edu" xr:uid="{D142A2B2-2FC6-4F88-84EB-459E84E21AC8}"/>
+    <hyperlink ref="J314" r:id="rId51" xr:uid="{A88778FF-CC52-4A9B-AC10-FBF8F003482B}"/>
+    <hyperlink ref="J313" r:id="rId52" display="mailto:rexrosario_ph2@mail.sjctni.edu" xr:uid="{02E9D1FC-4AA3-4692-896E-A3BDF0BE05B5}"/>
+    <hyperlink ref="J312" r:id="rId53" display="mailto:genifersilvena_ph2@mail.sjctni.edu" xr:uid="{2885B73C-64D3-4DD2-94F9-0C6BD170E997}"/>
+    <hyperlink ref="J311" r:id="rId54" display="mailto:augustin_ph2@mail.sjctni.edu" xr:uid="{8BBE3203-CF46-49C7-924B-76E7C3F6BA60}"/>
+    <hyperlink ref="J310" r:id="rId55" xr:uid="{48B90131-A1FC-4664-AE28-0E36C27F27F2}"/>
+    <hyperlink ref="J309" r:id="rId56" display="mailto:marydayana_ph2@mail.sjctni.edu" xr:uid="{1ADA392F-1DB7-45BC-AF35-28E902D09B00}"/>
+    <hyperlink ref="J308" r:id="rId57" display="mailto:sinthiya_ph2@mail.sjctni.edu" xr:uid="{CC18D803-8EF1-4776-9026-D8D681F09D2A}"/>
+    <hyperlink ref="J307" r:id="rId58" display="mailto:adalarasu_ph2@mail.sjctni.edu" xr:uid="{4924706F-6BB7-45FB-81EA-D14242C654E9}"/>
+    <hyperlink ref="J306" r:id="rId59" display="mailto:lourduraj_ph2@mail.sjctni.edu" xr:uid="{2ADF6A09-0EAF-4882-8858-F0627CE6955A}"/>
+    <hyperlink ref="J305" r:id="rId60" display="mailto:alexandar_ph1@mail.sjctni.edu" xr:uid="{A16B5392-E809-43DA-A116-1B32FB1294AE}"/>
+    <hyperlink ref="J304" r:id="rId61" display="mailto:prathaps_ph1@mail.sjctni.edu" xr:uid="{DC7F01D7-8D92-4141-BB19-A1A1FF5EFC9E}"/>
+    <hyperlink ref="J303" r:id="rId62" display="mailto:thomasr_ph1@mail.sjctni.edu" xr:uid="{A10B6E28-32A4-4B1E-9A6B-A7EA32A49340}"/>
+    <hyperlink ref="J302" r:id="rId63" display="mailto:joyprabu_ph2@mail.sjctni.edu" xr:uid="{74E710CF-3684-4FB6-B014-BE13EEC77422}"/>
+    <hyperlink ref="J301" r:id="rId64" display="mailto:samuel_ph1@mail.sjctni.edu" xr:uid="{DA8912AE-022B-46D2-8916-BCE1972E9492}"/>
+    <hyperlink ref="J300" r:id="rId65" display="mailto:antonyraj_ph1@mail.sjctni.edu" xr:uid="{27DB355E-49F2-410A-9F9E-BDDF58198A6B}"/>
+    <hyperlink ref="J299" r:id="rId66" display="mailto:anbarasu_ph1@mail.sjctni.edu" xr:uid="{9265CE46-B1F2-4697-B87D-BBBE9A7982A1}"/>
+    <hyperlink ref="J298" r:id="rId67" display="mailto:dinakaran_ph1@mail.sjctni.edu" xr:uid="{EB33C7C6-5D23-44C2-A8DE-B55D9374489A}"/>
+    <hyperlink ref="J297" r:id="rId68" display="mailto:jeraldvijay_ph1@mail.sjctni.edu" xr:uid="{561368F0-A622-4BAB-B9A5-3CA124A1A1C5}"/>
+    <hyperlink ref="J296" r:id="rId69" display="mailto:antonyarockiaraj_ph1@mail.sjctni.edu" xr:uid="{415FE73F-5F8A-46B0-A760-89EADF8DA138}"/>
+    <hyperlink ref="J295" r:id="rId70" display="mailto:clementlourduraj_ph1@mail.sjctni.edu" xr:uid="{AC1776E9-055E-488A-A0A9-8E709B50DB1F}"/>
+    <hyperlink ref="J294" r:id="rId71" display="mailto:armstrongarasu_ph1@mail.sjctni.edu" xr:uid="{419EED2D-86CF-4C0A-9A33-EB50E111DE91}"/>
+    <hyperlink ref="J293" r:id="rId72" display="mailto:maggiedayana_ph1@mail.sjctni.edu" xr:uid="{132719D8-060D-402D-9D4D-6C6DB9605CFE}"/>
+    <hyperlink ref="J292" r:id="rId73" display="mailto:christuraj_ph1@mail.sjctni.edu" xr:uid="{35E2E9CB-0FF5-43A8-8A2B-AD81A0635AC7}"/>
+    <hyperlink ref="J291" r:id="rId74" display="mailto:charles_ph1@mail.sjctni.edu" xr:uid="{8594491B-D151-4F0D-A859-40B74EC40715}"/>
+    <hyperlink ref="J290" r:id="rId75" display="mailto:kanickairaj_ph1@mail.sjctni.edu" xr:uid="{6DEA60E9-E59A-430A-B209-6506C688C734}"/>
+    <hyperlink ref="J289" r:id="rId76" display="mailto:johnson_ph1@mail.sjctni.edu" xr:uid="{D142A2B2-2FC6-4F88-84EB-459E84E21AC8}"/>
     <hyperlink ref="J288" r:id="rId77" xr:uid="{647AA566-EE3B-4B43-A082-BB1EA3CA893F}"/>
     <hyperlink ref="J286" r:id="rId78" display="mailto:sappanimuthu_el2@mail.sjctni.edu" xr:uid="{9ABCC02C-9595-4A7C-8B09-C6214BD5F46D}"/>
-    <hyperlink ref="J284" r:id="rId79" display="mailto:el2@mail.sjctni.edu" xr:uid="{9DF19201-AC44-479B-9395-B6C34E777494}"/>
-    <hyperlink ref="J283" r:id="rId80" display="mailto:el2@mail.sjctni.edu" xr:uid="{607C73B3-C8D2-4CCB-A7F7-38617AC296E2}"/>
-    <hyperlink ref="J280" r:id="rId81" display="mailto:johnwilson_el2@mail.sjctni.edu" xr:uid="{DE8EC69A-223F-4571-9869-4D5A637F5755}"/>
-    <hyperlink ref="J285" r:id="rId82" display="mailto:el2@mail.sjctni.edu" xr:uid="{822C5D0C-AE2B-44D2-9DC3-432A1FD212BA}"/>
-    <hyperlink ref="J282" r:id="rId83" display="mailto:manickam_el2@mail.sjctni.edu" xr:uid="{AAA37099-4031-449F-B361-531FCF7813DE}"/>
-    <hyperlink ref="J281" r:id="rId84" display="mailto:subbuthai_el2@mail.sjctni.edu" xr:uid="{10AB0058-00F9-423D-B4F5-AC14A63E5131}"/>
-    <hyperlink ref="J277" r:id="rId85" display="mailto:alphonsajuliethelina_ch2@mail.sjctni.edu" xr:uid="{F350C340-2A88-422A-9DFC-FC3AC832B388}"/>
-    <hyperlink ref="J271" r:id="rId86" display="mailto:arockiadoss_ch2@mail.sjctni.edu" xr:uid="{7029363D-847F-467E-A740-36750B0B0F2B}"/>
-    <hyperlink ref="J278" r:id="rId87" display="mailto:arunjosephrosario_ch1@mail.sjctni.edu" xr:uid="{E9CF7F73-4058-4A03-8C3B-5382E975AA98}"/>
-    <hyperlink ref="J276" r:id="rId88" display="mailto:rajasekaransj_ch1@mail.sjctni.edu" xr:uid="{F3C2DB22-4030-4405-B6F1-37DBCBB61CAF}"/>
-    <hyperlink ref="J275" r:id="rId89" display="mailto:sebastinthangadurai_ch1@mail.sjctni.edu" xr:uid="{12597E4E-F6D2-474E-96BB-06C0D80A88DC}"/>
-    <hyperlink ref="J274" r:id="rId90" display="mailto:arockiaraj_ch1@mail.sjctni.edu" xr:uid="{9C4206B3-1662-40E4-8E62-C12835393121}"/>
-    <hyperlink ref="J273" r:id="rId91" display="mailto:arunviveke_ch1@mail.sjctni.edu" xr:uid="{09D25935-07CE-4043-ABF6-49646B7BCB2B}"/>
-    <hyperlink ref="J272" r:id="rId92" display="mailto:leostandly_ch1@mail.sjctni.edu" xr:uid="{423F1BD3-7AD4-4A4B-B601-9665E4E28618}"/>
+    <hyperlink ref="J285" r:id="rId79" display="mailto:el2@mail.sjctni.edu" xr:uid="{9DF19201-AC44-479B-9395-B6C34E777494}"/>
+    <hyperlink ref="J284" r:id="rId80" display="mailto:el2@mail.sjctni.edu" xr:uid="{607C73B3-C8D2-4CCB-A7F7-38617AC296E2}"/>
+    <hyperlink ref="J282" r:id="rId81" display="mailto:johnwilson_el2@mail.sjctni.edu" xr:uid="{DE8EC69A-223F-4571-9869-4D5A637F5755}"/>
+    <hyperlink ref="J283" r:id="rId82" display="mailto:el2@mail.sjctni.edu" xr:uid="{822C5D0C-AE2B-44D2-9DC3-432A1FD212BA}"/>
+    <hyperlink ref="J281" r:id="rId83" display="mailto:manickam_el2@mail.sjctni.edu" xr:uid="{AAA37099-4031-449F-B361-531FCF7813DE}"/>
+    <hyperlink ref="J280" r:id="rId84" display="mailto:subbuthai_el2@mail.sjctni.edu" xr:uid="{10AB0058-00F9-423D-B4F5-AC14A63E5131}"/>
+    <hyperlink ref="J278" r:id="rId85" display="mailto:alphonsajuliethelina_ch2@mail.sjctni.edu" xr:uid="{F350C340-2A88-422A-9DFC-FC3AC832B388}"/>
+    <hyperlink ref="J277" r:id="rId86" display="mailto:arockiadoss_ch2@mail.sjctni.edu" xr:uid="{7029363D-847F-467E-A740-36750B0B0F2B}"/>
+    <hyperlink ref="J276" r:id="rId87" display="mailto:arunjosephrosario_ch1@mail.sjctni.edu" xr:uid="{E9CF7F73-4058-4A03-8C3B-5382E975AA98}"/>
+    <hyperlink ref="J275" r:id="rId88" display="mailto:rajasekaransj_ch1@mail.sjctni.edu" xr:uid="{F3C2DB22-4030-4405-B6F1-37DBCBB61CAF}"/>
+    <hyperlink ref="J274" r:id="rId89" display="mailto:sebastinthangadurai_ch1@mail.sjctni.edu" xr:uid="{12597E4E-F6D2-474E-96BB-06C0D80A88DC}"/>
+    <hyperlink ref="J273" r:id="rId90" display="mailto:arockiaraj_ch1@mail.sjctni.edu" xr:uid="{9C4206B3-1662-40E4-8E62-C12835393121}"/>
+    <hyperlink ref="J272" r:id="rId91" display="mailto:arunviveke_ch1@mail.sjctni.edu" xr:uid="{09D25935-07CE-4043-ABF6-49646B7BCB2B}"/>
+    <hyperlink ref="J271" r:id="rId92" display="mailto:leostandly_ch1@mail.sjctni.edu" xr:uid="{423F1BD3-7AD4-4A4B-B601-9665E4E28618}"/>
     <hyperlink ref="J270" r:id="rId93" display="mailto:mangalaraj_ch1@mail.sjctni.edu" xr:uid="{E6C8F91E-2A45-4B4F-8EBB-BAD7378F63A2}"/>
     <hyperlink ref="J269" r:id="rId94" display="mailto:rajarathinam_ch1@mail.sjctni.edu" xr:uid="{30B45450-4BB3-4054-AFE3-F8E28A3AC878}"/>
     <hyperlink ref="J268" r:id="rId95" display="mailto:ceriljeoffrey_ch1@mail.sjctni.edu" xr:uid="{6F1D15A6-1E50-4D39-AC03-975C98222203}"/>
@@ -13089,12 +13089,12 @@
     <hyperlink ref="J251" r:id="rId108" display="mailto:ramya_vc2@mail.sjctni.edu" xr:uid="{4B048C1A-8643-40D6-85FA-2076E2910D0D}"/>
     <hyperlink ref="J250" r:id="rId109" display="mailto:tamilarasi_vt1@mail.sjctni.edu" xr:uid="{937095CC-231D-4BB3-8D43-D63E75ED216B}"/>
     <hyperlink ref="J245" r:id="rId110" xr:uid="{A4697024-A05A-4137-9854-CFEDF0124334}"/>
-    <hyperlink ref="J239" r:id="rId111" xr:uid="{0785A0E9-CAC5-4D9E-8BBC-80073118379A}"/>
-    <hyperlink ref="J242" r:id="rId112" xr:uid="{B0F7F5B7-7CC0-4BF7-9BF1-833808A321A3}"/>
-    <hyperlink ref="J244" r:id="rId113" xr:uid="{C647EDBE-1E6D-46F2-B4D5-657385484235}"/>
-    <hyperlink ref="J243" r:id="rId114" xr:uid="{1D9A4A3D-F0C4-452C-8F2E-63435C45115D}"/>
+    <hyperlink ref="J244" r:id="rId111" xr:uid="{0785A0E9-CAC5-4D9E-8BBC-80073118379A}"/>
+    <hyperlink ref="J243" r:id="rId112" xr:uid="{B0F7F5B7-7CC0-4BF7-9BF1-833808A321A3}"/>
+    <hyperlink ref="J240" r:id="rId113" xr:uid="{C647EDBE-1E6D-46F2-B4D5-657385484235}"/>
+    <hyperlink ref="J242" r:id="rId114" xr:uid="{1D9A4A3D-F0C4-452C-8F2E-63435C45115D}"/>
     <hyperlink ref="J241" r:id="rId115" xr:uid="{6B6EA555-BE8C-4C37-A8AE-10B2E8AFCE9B}"/>
-    <hyperlink ref="J240" r:id="rId116" xr:uid="{5B795242-BD56-4E68-BBB1-79A2E3CEF088}"/>
+    <hyperlink ref="J239" r:id="rId116" xr:uid="{5B795242-BD56-4E68-BBB1-79A2E3CEF088}"/>
     <hyperlink ref="J238" r:id="rId117" xr:uid="{8045BA05-56B6-487A-B64D-1A71F79F8B2B}"/>
     <hyperlink ref="J237" r:id="rId118" xr:uid="{77DD1FCD-2DE7-4C66-B8B5-9EE04F2B20C9}"/>
     <hyperlink ref="J236" r:id="rId119" xr:uid="{9C282BD0-29A3-43AC-A2C5-3E4BF22E5894}"/>
@@ -13103,13 +13103,13 @@
     <hyperlink ref="J233" r:id="rId122" xr:uid="{99F1D4FA-9580-474D-B566-9F6281F296FE}"/>
     <hyperlink ref="J232" r:id="rId123" xr:uid="{634D537D-01D7-4249-B07F-EF3092B9B9C0}"/>
     <hyperlink ref="J231" r:id="rId124" xr:uid="{B665935B-BB84-4965-A14E-1B31166F2C51}"/>
-    <hyperlink ref="J229" r:id="rId125" xr:uid="{10DE6704-03DB-4465-8BC7-48203E0217BE}"/>
-    <hyperlink ref="J230" r:id="rId126" xr:uid="{A4613E7A-9463-4462-8F59-A512B4255290}"/>
+    <hyperlink ref="J230" r:id="rId125" xr:uid="{10DE6704-03DB-4465-8BC7-48203E0217BE}"/>
+    <hyperlink ref="J229" r:id="rId126" xr:uid="{A4613E7A-9463-4462-8F59-A512B4255290}"/>
     <hyperlink ref="J227" r:id="rId127" xr:uid="{D33632BB-DF7F-4B45-9576-A8508F59DEFC}"/>
     <hyperlink ref="J228" r:id="rId128" xr:uid="{F869BE81-4E05-4F38-A133-6E5BF969FB15}"/>
     <hyperlink ref="J226" r:id="rId129" xr:uid="{6875E799-614C-4AB3-8780-0922B9522666}"/>
     <hyperlink ref="J222" r:id="rId130" display="mailto:rinaldodedavid_bu2@mail.sjctni.edu" xr:uid="{AF08C07C-5D59-4523-8A79-CDD94B171E91}"/>
-    <hyperlink ref="J221" r:id="rId131" display="mailto:arputharaj_bu2@mail.sjctni.edu" xr:uid="{7FD61564-BEC0-4E87-B900-BCAEF9500CC0}"/>
+    <hyperlink ref="J220" r:id="rId131" display="mailto:arputharaj_bu2@mail.sjctni.edu" xr:uid="{7FD61564-BEC0-4E87-B900-BCAEF9500CC0}"/>
     <hyperlink ref="J218" r:id="rId132" xr:uid="{DEB34283-28ED-4770-B65C-A1873FA957EC}"/>
     <hyperlink ref="J219" r:id="rId133" xr:uid="{DAB3988E-5E75-4F85-B284-B64DD0BFD002}"/>
     <hyperlink ref="J213" r:id="rId134" xr:uid="{8556D2F8-D11D-4824-B762-7721AC1FD90F}"/>
@@ -13119,24 +13119,24 @@
     <hyperlink ref="J214" r:id="rId138" display="mailto:johnkennedy_ta2@mail.sjctni.edu" xr:uid="{2B59A847-51C5-4978-B44C-DE78983ED8FF}"/>
     <hyperlink ref="J212" r:id="rId139" display="mailto:dhanalakshmi_ta2@mail.sjctni.edu" xr:uid="{F1DC81E2-E20D-44B6-9A71-215A7125A8C3}"/>
     <hyperlink ref="J211" r:id="rId140" display="mailto:ta2@mail.sjctni.edu" xr:uid="{73BD82CF-3EE2-4F8E-BF80-F7471113C286}"/>
-    <hyperlink ref="J206" r:id="rId141" display="mailto:johnson_ta2@mail.sjctni.edu" xr:uid="{DA6B480D-1AA3-4BC1-9BB5-40BE4EA171B4}"/>
-    <hyperlink ref="J205" r:id="rId142" xr:uid="{052C0483-CB0D-457C-A59B-C869E0EA1531}"/>
-    <hyperlink ref="J204" r:id="rId143" display="mailto:yogaraj_ta2@mail.sjctni.edu" xr:uid="{48A44C89-D449-48F2-BF1F-B4399737318B}"/>
-    <hyperlink ref="J202" r:id="rId144" display="mailto:muralikrishnan_ta2@mail.sjctni.edu" xr:uid="{7C4AFEF5-D0C8-4812-9E79-516966A98D07}"/>
-    <hyperlink ref="J201" r:id="rId145" display="mailto:srinivasan_ta1@mail.sjctni.edu" xr:uid="{7D2D690D-689B-4A71-8BE5-62DCFF148E99}"/>
-    <hyperlink ref="J196" r:id="rId146" display="mailto:backyaselvarathi_ta2@mail.sjctni.edu" xr:uid="{F8842DB0-5EB5-4B7A-AADC-44FB19E58C70}"/>
-    <hyperlink ref="J194" r:id="rId147" display="mailto:arockiadhanaraj_ta1@mail.sjctni.edu" xr:uid="{1852F2B8-F0B8-4EED-8042-F8715B1DF28B}"/>
-    <hyperlink ref="J210" r:id="rId148" display="mailto:adaikkalaraj_ta2@mail.sjctni.edu" xr:uid="{D1B9554E-5D08-4F40-AED4-D887F2E25103}"/>
-    <hyperlink ref="J209" r:id="rId149" display="mailto:adaikkalaraj_ta2@mail.sjctni.edu" xr:uid="{56F956B4-5FD8-47BA-9D3F-5CC3361FF379}"/>
-    <hyperlink ref="J208" r:id="rId150" display="mailto:nallamuthu_ta2@mail.sjctni.edu" xr:uid="{1CBF8CC8-F1F9-46B8-9399-8A4ECE76324E}"/>
-    <hyperlink ref="J207" r:id="rId151" display="mailto:nallamuthu_ta2@mail.sjctni.edu" xr:uid="{61E40FD3-591C-47AF-924F-BD9E4DBFF10E}"/>
-    <hyperlink ref="J203" r:id="rId152" display="mailto:mariadhanabal_ta1@mail.sjctni.edu" xr:uid="{C4F56A7F-B409-4F46-82C3-C1B00A025B76}"/>
-    <hyperlink ref="J200" r:id="rId153" display="mailto:shagilabanu_ta1@mail.sjctni.edu" xr:uid="{9B88E84E-C560-4EA1-BBB6-C2113C7DA726}"/>
-    <hyperlink ref="J199" r:id="rId154" display="mailto:rajathi_ta1@mail.sjctni.edu" xr:uid="{671E23AE-A647-4455-85FE-7FA61B1F4791}"/>
-    <hyperlink ref="J198" r:id="rId155" display="mailto:benjaminarontitus_ta1@mail.sjctni.edu" xr:uid="{793297DC-BA82-4674-B1AD-440C72A3F408}"/>
-    <hyperlink ref="J197" r:id="rId156" display="mailto:wilson_ta1@mail.sjctni.edu" xr:uid="{D0AA4CE0-6A9D-479F-87E1-F0AEB3EE3B1A}"/>
-    <hyperlink ref="J193" r:id="rId157" display="mailto:beschi_ta1@mail.sjctni.edu" xr:uid="{5CCA4BF7-C750-41FF-84EB-727B40CADA3C}"/>
-    <hyperlink ref="J195" r:id="rId158" display="mailto:josephsahayaraj_ta1@mail.sjctni.edu" xr:uid="{F85BB417-E6F6-4A6A-981C-E591F9A16255}"/>
+    <hyperlink ref="J210" r:id="rId141" display="mailto:johnson_ta2@mail.sjctni.edu" xr:uid="{DA6B480D-1AA3-4BC1-9BB5-40BE4EA171B4}"/>
+    <hyperlink ref="J209" r:id="rId142" xr:uid="{052C0483-CB0D-457C-A59B-C869E0EA1531}"/>
+    <hyperlink ref="J208" r:id="rId143" display="mailto:yogaraj_ta2@mail.sjctni.edu" xr:uid="{48A44C89-D449-48F2-BF1F-B4399737318B}"/>
+    <hyperlink ref="J207" r:id="rId144" display="mailto:muralikrishnan_ta2@mail.sjctni.edu" xr:uid="{7C4AFEF5-D0C8-4812-9E79-516966A98D07}"/>
+    <hyperlink ref="J206" r:id="rId145" display="mailto:srinivasan_ta1@mail.sjctni.edu" xr:uid="{7D2D690D-689B-4A71-8BE5-62DCFF148E99}"/>
+    <hyperlink ref="J205" r:id="rId146" display="mailto:backyaselvarathi_ta2@mail.sjctni.edu" xr:uid="{F8842DB0-5EB5-4B7A-AADC-44FB19E58C70}"/>
+    <hyperlink ref="J204" r:id="rId147" display="mailto:arockiadhanaraj_ta1@mail.sjctni.edu" xr:uid="{1852F2B8-F0B8-4EED-8042-F8715B1DF28B}"/>
+    <hyperlink ref="J203" r:id="rId148" display="mailto:adaikkalaraj_ta2@mail.sjctni.edu" xr:uid="{D1B9554E-5D08-4F40-AED4-D887F2E25103}"/>
+    <hyperlink ref="J202" r:id="rId149" display="mailto:adaikkalaraj_ta2@mail.sjctni.edu" xr:uid="{56F956B4-5FD8-47BA-9D3F-5CC3361FF379}"/>
+    <hyperlink ref="J201" r:id="rId150" display="mailto:nallamuthu_ta2@mail.sjctni.edu" xr:uid="{1CBF8CC8-F1F9-46B8-9399-8A4ECE76324E}"/>
+    <hyperlink ref="J200" r:id="rId151" display="mailto:nallamuthu_ta2@mail.sjctni.edu" xr:uid="{61E40FD3-591C-47AF-924F-BD9E4DBFF10E}"/>
+    <hyperlink ref="J199" r:id="rId152" display="mailto:mariadhanabal_ta1@mail.sjctni.edu" xr:uid="{C4F56A7F-B409-4F46-82C3-C1B00A025B76}"/>
+    <hyperlink ref="J198" r:id="rId153" display="mailto:shagilabanu_ta1@mail.sjctni.edu" xr:uid="{9B88E84E-C560-4EA1-BBB6-C2113C7DA726}"/>
+    <hyperlink ref="J197" r:id="rId154" display="mailto:rajathi_ta1@mail.sjctni.edu" xr:uid="{671E23AE-A647-4455-85FE-7FA61B1F4791}"/>
+    <hyperlink ref="J196" r:id="rId155" display="mailto:benjaminarontitus_ta1@mail.sjctni.edu" xr:uid="{793297DC-BA82-4674-B1AD-440C72A3F408}"/>
+    <hyperlink ref="J195" r:id="rId156" display="mailto:wilson_ta1@mail.sjctni.edu" xr:uid="{D0AA4CE0-6A9D-479F-87E1-F0AEB3EE3B1A}"/>
+    <hyperlink ref="J194" r:id="rId157" display="mailto:beschi_ta1@mail.sjctni.edu" xr:uid="{5CCA4BF7-C750-41FF-84EB-727B40CADA3C}"/>
+    <hyperlink ref="J193" r:id="rId158" display="mailto:josephsahayaraj_ta1@mail.sjctni.edu" xr:uid="{F85BB417-E6F6-4A6A-981C-E591F9A16255}"/>
     <hyperlink ref="J192" r:id="rId159" display="mailto:madhavachari_sa1@mail.sjctni.edu" xr:uid="{463055AF-39BE-4F54-B64D-EDE77139D31D}"/>
     <hyperlink ref="J184" r:id="rId160" xr:uid="{3924F3E1-5CAF-49F7-B96F-E12CC9EC849F}"/>
     <hyperlink ref="J183" r:id="rId161" display="mailto:mohanalakshmi_fr1@mail.sjctni.edu" xr:uid="{9DB734F6-B628-4938-A7A7-22222A2DE1A0}"/>
@@ -13146,28 +13146,28 @@
     <hyperlink ref="J178" r:id="rId165" xr:uid="{C44C77DE-A3F3-4E9C-9173-CE21D74A4138}"/>
     <hyperlink ref="J177" r:id="rId166" xr:uid="{87C827F2-BE10-4B48-8413-F57BF89E83CA}"/>
     <hyperlink ref="J176" r:id="rId167" xr:uid="{08812211-A6A2-4B01-BF4F-E8B5AC1E38FD}"/>
-    <hyperlink ref="J171" r:id="rId168" xr:uid="{A1357B33-B88C-47FD-AA1F-C2625D35C932}"/>
-    <hyperlink ref="J173" r:id="rId169" xr:uid="{5C403D75-1F09-45B1-8C55-46605EE792A3}"/>
-    <hyperlink ref="J172" r:id="rId170" xr:uid="{82D6DE37-200C-4550-92E8-A2C5870E1F7F}"/>
-    <hyperlink ref="J169" r:id="rId171" xr:uid="{C1394099-CE1A-4AEA-888C-DC8163B0B575}"/>
-    <hyperlink ref="J168" r:id="rId172" xr:uid="{AD1B10B0-21FA-4549-94EF-912AFB1E4CCF}"/>
-    <hyperlink ref="J166" r:id="rId173" xr:uid="{4554FC5D-3148-480B-8E3D-CFC9EF97F8FE}"/>
-    <hyperlink ref="J157" r:id="rId174" xr:uid="{5C9E10E8-A54B-481C-B243-6BD3FDCF7174}"/>
-    <hyperlink ref="J156" r:id="rId175" xr:uid="{CFF962C0-0282-4FE4-81EB-F26B1B23600C}"/>
-    <hyperlink ref="J155" r:id="rId176" xr:uid="{B73BFD2B-004E-42E1-BAE6-0C7E42B2C946}"/>
-    <hyperlink ref="J154" r:id="rId177" xr:uid="{C47ED2A3-7F4A-4277-BB65-8675EC9C2301}"/>
+    <hyperlink ref="J175" r:id="rId168" xr:uid="{A1357B33-B88C-47FD-AA1F-C2625D35C932}"/>
+    <hyperlink ref="J174" r:id="rId169" xr:uid="{5C403D75-1F09-45B1-8C55-46605EE792A3}"/>
+    <hyperlink ref="J173" r:id="rId170" xr:uid="{82D6DE37-200C-4550-92E8-A2C5870E1F7F}"/>
+    <hyperlink ref="J172" r:id="rId171" xr:uid="{C1394099-CE1A-4AEA-888C-DC8163B0B575}"/>
+    <hyperlink ref="J171" r:id="rId172" xr:uid="{AD1B10B0-21FA-4549-94EF-912AFB1E4CCF}"/>
+    <hyperlink ref="J170" r:id="rId173" xr:uid="{4554FC5D-3148-480B-8E3D-CFC9EF97F8FE}"/>
+    <hyperlink ref="J168" r:id="rId174" xr:uid="{5C9E10E8-A54B-481C-B243-6BD3FDCF7174}"/>
+    <hyperlink ref="J169" r:id="rId175" xr:uid="{CFF962C0-0282-4FE4-81EB-F26B1B23600C}"/>
+    <hyperlink ref="J167" r:id="rId176" xr:uid="{B73BFD2B-004E-42E1-BAE6-0C7E42B2C946}"/>
+    <hyperlink ref="J166" r:id="rId177" xr:uid="{C47ED2A3-7F4A-4277-BB65-8675EC9C2301}"/>
     <hyperlink ref="J165" r:id="rId178" xr:uid="{51E7B6C3-BCB9-4BB7-AB8C-2ED61AD92375}"/>
-    <hyperlink ref="J175" r:id="rId179" xr:uid="{76708A20-EA62-41AF-9B33-E405EA143CBF}"/>
-    <hyperlink ref="J174" r:id="rId180" xr:uid="{A79BEDB0-B8AA-4810-A8AB-28EE13720ED8}"/>
-    <hyperlink ref="J170" r:id="rId181" xr:uid="{93258349-FC4B-4ADD-B362-0BF0AD842225}"/>
-    <hyperlink ref="J167" r:id="rId182" xr:uid="{953F6F4A-987E-41DB-BB7D-2A3BBB1C99E4}"/>
-    <hyperlink ref="J164" r:id="rId183" xr:uid="{20461BB6-3AED-4CBB-BE86-83B7C31F564E}"/>
-    <hyperlink ref="J160" r:id="rId184" xr:uid="{05EC1B68-4756-4F26-AE28-B09078556FA4}"/>
-    <hyperlink ref="J163" r:id="rId185" xr:uid="{41D196EC-06E4-4722-9ABF-6286A64D443A}"/>
-    <hyperlink ref="J162" r:id="rId186" xr:uid="{612CDB9B-D170-4107-A90A-DE81F50A716D}"/>
-    <hyperlink ref="J161" r:id="rId187" xr:uid="{C7E258A4-AE77-4856-93A0-91F9C952A88C}"/>
-    <hyperlink ref="J159" r:id="rId188" xr:uid="{B092AF05-C129-4F30-AF02-E538D5AAA2A4}"/>
-    <hyperlink ref="J158" r:id="rId189" xr:uid="{1797ADEB-1E53-48D4-AA2F-C8CA01BF0045}"/>
+    <hyperlink ref="J164" r:id="rId179" xr:uid="{76708A20-EA62-41AF-9B33-E405EA143CBF}"/>
+    <hyperlink ref="J163" r:id="rId180" xr:uid="{A79BEDB0-B8AA-4810-A8AB-28EE13720ED8}"/>
+    <hyperlink ref="J162" r:id="rId181" xr:uid="{93258349-FC4B-4ADD-B362-0BF0AD842225}"/>
+    <hyperlink ref="J161" r:id="rId182" xr:uid="{953F6F4A-987E-41DB-BB7D-2A3BBB1C99E4}"/>
+    <hyperlink ref="J160" r:id="rId183" xr:uid="{20461BB6-3AED-4CBB-BE86-83B7C31F564E}"/>
+    <hyperlink ref="J159" r:id="rId184" xr:uid="{05EC1B68-4756-4F26-AE28-B09078556FA4}"/>
+    <hyperlink ref="J158" r:id="rId185" xr:uid="{41D196EC-06E4-4722-9ABF-6286A64D443A}"/>
+    <hyperlink ref="J157" r:id="rId186" xr:uid="{612CDB9B-D170-4107-A90A-DE81F50A716D}"/>
+    <hyperlink ref="J156" r:id="rId187" xr:uid="{C7E258A4-AE77-4856-93A0-91F9C952A88C}"/>
+    <hyperlink ref="J155" r:id="rId188" xr:uid="{B092AF05-C129-4F30-AF02-E538D5AAA2A4}"/>
+    <hyperlink ref="J154" r:id="rId189" xr:uid="{1797ADEB-1E53-48D4-AA2F-C8CA01BF0045}"/>
     <hyperlink ref="J153" r:id="rId190" xr:uid="{F784D162-BBA1-44F7-A8EA-3D8563324E79}"/>
     <hyperlink ref="J152" r:id="rId191" xr:uid="{84140522-145B-445C-BE5A-CC41A560AA75}"/>
     <hyperlink ref="J151" r:id="rId192" xr:uid="{83173254-5E59-4F0F-93B1-C4FB1017F8B5}"/>
@@ -13181,92 +13181,92 @@
     <hyperlink ref="J143" r:id="rId200" display="mailto:glorypersial_st1@mail.sjctni.edu" xr:uid="{ED8F8BBF-AC35-4745-B113-2E6AD7DB79DB}"/>
     <hyperlink ref="J142" r:id="rId201" display="mailto:vijayakumar_st1@mail.sjctni.edu" xr:uid="{7C80241C-C293-49B2-8F4B-013ABAA0EB42}"/>
     <hyperlink ref="J139" r:id="rId202" display="mailto:arulxavier_ma2@mail.sjctni.edu" xr:uid="{9AA0DE98-9D22-4FF0-998D-6CA1F58415A7}"/>
-    <hyperlink ref="J137" r:id="rId203" display="mailto:sahayajernith_ma2@mail.sjctni.edu" xr:uid="{453ACA05-4C33-4C76-9583-99CAD6DE41AB}"/>
-    <hyperlink ref="J136" r:id="rId204" display="mailto:saral_ma2@mail.sjctni.edu" xr:uid="{F8A5E53E-E810-4103-A8A8-73BBBDEF1C8E}"/>
-    <hyperlink ref="J135" r:id="rId205" display="mailto:jairoselin_ma2@mail.sjctni.edu" xr:uid="{511CCE8C-EF96-473E-8599-2C03DFBD8A20}"/>
-    <hyperlink ref="J138" r:id="rId206" display="mailto:delman_ma2@mail.sjctni.edu" xr:uid="{782AC4AE-F618-4859-AF92-74C1BF07E94E}"/>
-    <hyperlink ref="J119" r:id="rId207" display="mailto:mercyarokiarani_ma2@mail.sjctni.edu" xr:uid="{24CF2D0D-88F8-4637-9E03-5958F2B64487}"/>
-    <hyperlink ref="J118" r:id="rId208" display="mailto:lawrencerozarioraj_ma2@mail.sjctni.edu" xr:uid="{73E96C0C-7FB2-436A-A715-4F4B32C90710}"/>
-    <hyperlink ref="J134" r:id="rId209" display="mailto:carmel_ma1@mail.sjctni.edu" xr:uid="{FECEDAF0-2060-4749-B60B-A2B74C948947}"/>
-    <hyperlink ref="J133" r:id="rId210" display="mailto:aseervatham_ma1@mail.sjctni.edu" xr:uid="{8CB86664-F516-4B53-AA00-8234387C9D3D}"/>
-    <hyperlink ref="J132" r:id="rId211" display="mailto:arulgnanapragasam_ma1@mail.sjctni.edu" xr:uid="{6B4224B3-20D0-454A-B9D2-9259DAA5FCEE}"/>
-    <hyperlink ref="J131" r:id="rId212" display="mailto:lenin_ma1@mail.sjctni.edu" xr:uid="{254C4AB7-74F0-489A-BA83-55AC5A8FFAFB}"/>
-    <hyperlink ref="J130" r:id="rId213" display="mailto:amalorpavajerline_ma1@mail.sjctni.edu" xr:uid="{1F04A7EA-5D5F-433D-9B3D-A10BEB463744}"/>
-    <hyperlink ref="J125" r:id="rId214" display="mailto:geethasivaraman_ma1@mail.sjctni.edu" xr:uid="{06591B5F-37C3-49B7-B045-67A9C811AD85}"/>
-    <hyperlink ref="J129" r:id="rId215" display="mailto:vairaperumal_ma1@mail.sjctni.edu" xr:uid="{E0D35E88-C344-455A-B49B-60C547E9491E}"/>
-    <hyperlink ref="J128" r:id="rId216" display="mailto:ithayaezhilmanna_ma1@mail.sjctni.edu" xr:uid="{9E1F6747-98B1-443A-8C2D-FC4E99107D85}"/>
-    <hyperlink ref="J127" r:id="rId217" display="mailto:arockiajeyakumar_ma1@mail.sjctni.edu" xr:uid="{6F88A29A-B470-48A2-8D78-9FE079ADE1B1}"/>
-    <hyperlink ref="J126" r:id="rId218" display="mailto:mariajoseph_ma1@mail.sjctni.edu" xr:uid="{DE6B2903-A87B-40E0-835B-D95547BDDFC8}"/>
-    <hyperlink ref="J124" r:id="rId219" display="mailto:christyroja_ma1@mail.sjctni.edu" xr:uid="{39C2FDF6-957A-4D4C-B167-C6F286F74369}"/>
-    <hyperlink ref="J123" r:id="rId220" display="mailto:praveen_ma1@mail.sjctni.edu" xr:uid="{43208E5C-EEF6-42C8-A7B6-47B2B4EDF75C}"/>
-    <hyperlink ref="J122" r:id="rId221" display="mailto:anthonyeldred_ma1@mail.sjctni.edu" xr:uid="{B1D4AB80-EA5E-4FD1-BE6E-48E45C3E16F7}"/>
-    <hyperlink ref="J121" r:id="rId222" display="mailto:umamaheswari_ma1@mail.sjctni.edu" xr:uid="{5174DF08-E702-485E-BEAD-51FAA9167EF7}"/>
-    <hyperlink ref="J120" r:id="rId223" display="mailto:dominic_ma1@mail.sjctni.edu" xr:uid="{41323CAF-FD04-4336-B3BE-1048353ED732}"/>
-    <hyperlink ref="J117" r:id="rId224" display="mailto:thiagarajan_ma1@mail.sjctni.edu" xr:uid="{A7BC0D85-7061-4717-8208-13FC2733C418}"/>
-    <hyperlink ref="J116" r:id="rId225" xr:uid="{D17DDE0D-B6EA-4121-90E1-216D4D98D7F7}"/>
-    <hyperlink ref="J112" r:id="rId226" display="mailto:nikilprakasht_it2@mail.sjctni.edu" xr:uid="{ADAF7638-A205-45E7-ABED-7C3493880ED4}"/>
-    <hyperlink ref="J111" r:id="rId227" display="mailto:carol_cy2@mail.sjctni.edu" xr:uid="{9BF59017-19DC-4870-9C06-B3E56436ED20}"/>
-    <hyperlink ref="J110" r:id="rId228" display="mailto:richard_it2@mail.sjctni.edu" xr:uid="{7183D95B-1884-46DB-9000-F0C66F57B5EF}"/>
-    <hyperlink ref="J108" r:id="rId229" display="mailto:mangaibegum_cy2@mail.sjctni.edu" xr:uid="{A350E485-E431-4B54-ACF7-6D15DD0F365F}"/>
-    <hyperlink ref="J109" r:id="rId230" display="mailto:venishraja_cy2@mail.sjctni.edu" xr:uid="{51B74FF7-01E2-4693-8B95-9C93C86E1CD8}"/>
-    <hyperlink ref="J107" r:id="rId231" display="mailto:bastinthiyagaraj_cy2@mail.sjctni.edu" xr:uid="{A4E0B506-EF49-4520-8BF1-E3AE2439DD9F}"/>
-    <hyperlink ref="J106" r:id="rId232" display="mailto:mariaantoniatemartin_cy2@mail.sjctni.edu" xr:uid="{36ECB4A9-3A41-4C67-9CAE-CD358757C7B9}"/>
-    <hyperlink ref="J104" r:id="rId233" display="mailto:martin_it2@mail.sjctni.edu" xr:uid="{26A0A58A-ED20-4AB3-A00A-CB4D676B1245}"/>
-    <hyperlink ref="J105" r:id="rId234" display="mailto:antonyprakash_cy2@mail.sjctni.edu" xr:uid="{94AEC252-497F-4A75-86CA-769FB18DC131}"/>
-    <hyperlink ref="J101" r:id="rId235" display="mailto:beatricedorothy_ds2@mail.sjctni.edu" xr:uid="{ABEF7AEF-E4A5-4CDA-BBDA-910C6482657C}"/>
-    <hyperlink ref="J100" r:id="rId236" display="mailto:kriushanth_ds2@mail.sjctni.edu" xr:uid="{B12FA3D5-9552-4D53-A179-66704AC0F1C7}"/>
-    <hyperlink ref="J99" r:id="rId237" xr:uid="{39A1A6CA-822F-400E-994F-E1E36F78620C}"/>
-    <hyperlink ref="J102" r:id="rId238" display="mailto:rajaretnam_ds2@mail.sjctni.edu" xr:uid="{A24D0589-3D7A-4E6E-A264-C684553F5FD4}"/>
-    <hyperlink ref="J96" r:id="rId239" xr:uid="{61BC2AC1-63A9-4F8F-AC31-603C65B54F84}"/>
-    <hyperlink ref="J95" r:id="rId240" xr:uid="{C90445A0-51D4-43CB-A2BC-F8F158E85B1B}"/>
-    <hyperlink ref="J93" r:id="rId241" xr:uid="{9C32B9ED-F2CB-4BB5-9D28-D7A1F77951B3}"/>
-    <hyperlink ref="J94" r:id="rId242" xr:uid="{CBFEBBF1-EE15-45E1-BD65-5D71F79D6294}"/>
-    <hyperlink ref="J91" r:id="rId243" xr:uid="{2E14F8F6-D3E8-439F-B9E7-47B77FF35515}"/>
-    <hyperlink ref="J87" r:id="rId244" xr:uid="{B013F430-581A-453F-9FC7-0A4F8B7E9CDA}"/>
-    <hyperlink ref="J86" r:id="rId245" xr:uid="{D607720E-B4D2-4A71-AF89-9083D504C8FA}"/>
-    <hyperlink ref="J85" r:id="rId246" xr:uid="{93AF7A9D-BFB1-433B-AF8B-A51C1C1FD66F}"/>
-    <hyperlink ref="J78" r:id="rId247" xr:uid="{C2FA638B-067D-4805-8834-D8BD9F57E8C3}"/>
-    <hyperlink ref="J76" r:id="rId248" xr:uid="{F6AA06D5-F198-41F4-96F5-99F5231B71DD}"/>
-    <hyperlink ref="J92" r:id="rId249" xr:uid="{B4D56B07-6B58-44F6-B49F-535BF52A1869}"/>
-    <hyperlink ref="J90" r:id="rId250" xr:uid="{A7D3CD70-B34C-47FA-BDFD-73A5F50C79CD}"/>
-    <hyperlink ref="J89" r:id="rId251" xr:uid="{DDF9737F-DC21-423F-B7A8-99B3C32A32EC}"/>
-    <hyperlink ref="J88" r:id="rId252" xr:uid="{92A15F20-F04A-4F3E-A87C-03CAA937AA09}"/>
-    <hyperlink ref="J84" r:id="rId253" xr:uid="{5A59712E-C3DE-4A19-A8E8-C80AD15825A5}"/>
-    <hyperlink ref="J83" r:id="rId254" xr:uid="{D806A201-4DA8-42E6-BB02-93B65DDC61EE}"/>
-    <hyperlink ref="J82" r:id="rId255" xr:uid="{B784CC6B-ACA3-4A27-9EA5-02C761DCC28A}"/>
-    <hyperlink ref="J81" r:id="rId256" xr:uid="{CA1737B2-3F6F-407A-95FF-3E406CD81462}"/>
-    <hyperlink ref="J80" r:id="rId257" xr:uid="{17997236-0A0E-44A3-97BB-CD184BF4D697}"/>
-    <hyperlink ref="J79" r:id="rId258" xr:uid="{8CECA54A-A9FD-4DCA-B7DC-8687CFAF56B2}"/>
-    <hyperlink ref="J77" r:id="rId259" xr:uid="{FBF18AD3-14FF-4040-9D0D-E946595BD5AE}"/>
-    <hyperlink ref="J73" r:id="rId260" display="mailto:banumathi_ss1@mail.sjctni.edu" xr:uid="{D2664550-8230-4530-A353-B25EE0D9724D}"/>
-    <hyperlink ref="J72" r:id="rId261" display="mailto:janeva_ss1@mail.sjctni.edu" xr:uid="{D54C57E8-A68A-470C-90A3-E461BE46F4F2}"/>
-    <hyperlink ref="J71" r:id="rId262" display="mailto:genocinthia_ss1@mail.sjctni.edu" xr:uid="{E026B3D1-B944-43A1-B69A-FB0C03EEEEAB}"/>
-    <hyperlink ref="J69" r:id="rId263" xr:uid="{EE424ED9-F8D5-4B02-BB15-930578A44E11}"/>
-    <hyperlink ref="J66" r:id="rId264" xr:uid="{92812536-E14D-4695-8550-4A4684C2568B}"/>
-    <hyperlink ref="J65" r:id="rId265" xr:uid="{B0C41A4E-2D1B-41E2-9897-24CEFF2411E3}"/>
-    <hyperlink ref="J64" r:id="rId266" xr:uid="{C092E216-7F24-4F5C-AD8A-B38CEAB94A60}"/>
-    <hyperlink ref="J62" r:id="rId267" display="mailto:jerryrichards_cr2@mail.sjctni.edu" xr:uid="{3BF963B7-DBDE-4D7D-A7CA-B44AAAD62FFE}"/>
-    <hyperlink ref="J61" r:id="rId268" display="mailto:prabakaran_cr2@mail.sjctni.edu" xr:uid="{EBB06740-E339-4F9F-B639-15EE28DCA6D9}"/>
-    <hyperlink ref="J14" r:id="rId269" display="mailto:sahayasathish_bo1@mail.sjctni.edu" xr:uid="{40BF0A23-5B55-46B5-81B6-0C78B594CB65}"/>
-    <hyperlink ref="J12" r:id="rId270" xr:uid="{A196ADF3-3394-4FA6-B81F-C52F701897B9}"/>
-    <hyperlink ref="J11" r:id="rId271" xr:uid="{F5E43E46-2D93-416E-9527-CC138B4CEE73}"/>
-    <hyperlink ref="J10" r:id="rId272" xr:uid="{1D146766-B07E-452D-A0DE-679A8F07671E}"/>
-    <hyperlink ref="J9" r:id="rId273" xr:uid="{FCEB218A-35CB-46B5-B07E-EB292E601D02}"/>
-    <hyperlink ref="J7" r:id="rId274" xr:uid="{A7B9D8D4-619D-4208-9079-636944F6B4F0}"/>
-    <hyperlink ref="J8" r:id="rId275" xr:uid="{7374DC9D-C649-4289-9A58-4BF6E28A0F6A}"/>
-    <hyperlink ref="J5" r:id="rId276" xr:uid="{3B9C7A78-8E3A-4E1A-9EC1-C24351124236}"/>
-    <hyperlink ref="J6" r:id="rId277" display="mailto:geegi_bi2@mail.sjctni.edu" xr:uid="{A08901E5-BD66-41EF-9D30-BB9688C3CF53}"/>
-    <hyperlink ref="J4" r:id="rId278" xr:uid="{A14BB14D-6583-4E33-9CB5-845942840D30}"/>
-    <hyperlink ref="J23" r:id="rId279" display="mailto:bastinchurchill_bo1@mail.sjctni.edu" xr:uid="{D1B933E7-D7C5-49BD-A272-B4D47584BA96}"/>
-    <hyperlink ref="J22" r:id="rId280" display="mailto:anusuya_bo1@mail.sjctni.edu" xr:uid="{0A1445A1-76DC-4D4C-ABC5-A9BA36BCDD53}"/>
-    <hyperlink ref="J21" r:id="rId281" display="mailto:jktagore_bo1@mail.sjctni.edu" xr:uid="{3B4C2487-A290-47DC-BCF3-138BDA501E12}"/>
-    <hyperlink ref="J20" r:id="rId282" display="mailto:davidraja_bo1@mail.sjctni.edu" xr:uid="{C50EA119-02AA-4DF8-8FB2-E717F6D79235}"/>
-    <hyperlink ref="J19" r:id="rId283" display="mailto:johnpeterarulanandam_bo1@mail.sjctni.edu" xr:uid="{1C770BDC-DB3F-4F65-B81F-9AE8CA950210}"/>
-    <hyperlink ref="J18" r:id="rId284" display="mailto:francissathiyaseelan_bo1@mail.sjctni.edu" xr:uid="{31490BCB-CF27-4622-AFFF-796D034A5379}"/>
-    <hyperlink ref="J17" r:id="rId285" display="mailto:francisxavier_bo1@mail.sjctni.edu" xr:uid="{03DA3A05-46C5-496C-9D74-EC67A68CFA94}"/>
-    <hyperlink ref="J16" r:id="rId286" display="mailto:soosairaj_bo1@mail.sjctni.edu" xr:uid="{BB341FF9-6352-4D37-9EC4-F60D9999F099}"/>
-    <hyperlink ref="J15" r:id="rId287" display="mailto:egbertselwinrose_bo1@mail.sjctni.edu" xr:uid="{C6135AC3-71F3-4230-ACC5-1050601C87A6}"/>
-    <hyperlink ref="J13" r:id="rId288" display="mailto:senthilkumar_bo1@mail.sjctni.edu" xr:uid="{1F658893-B83F-407A-819D-BE536F1BE588}"/>
+    <hyperlink ref="J138" r:id="rId203" display="mailto:sahayajernith_ma2@mail.sjctni.edu" xr:uid="{453ACA05-4C33-4C76-9583-99CAD6DE41AB}"/>
+    <hyperlink ref="J137" r:id="rId204" display="mailto:saral_ma2@mail.sjctni.edu" xr:uid="{F8A5E53E-E810-4103-A8A8-73BBBDEF1C8E}"/>
+    <hyperlink ref="J135" r:id="rId205" display="mailto:delman_ma2@mail.sjctni.edu" xr:uid="{782AC4AE-F618-4859-AF92-74C1BF07E94E}"/>
+    <hyperlink ref="J134" r:id="rId206" display="mailto:mercyarokiarani_ma2@mail.sjctni.edu" xr:uid="{24CF2D0D-88F8-4637-9E03-5958F2B64487}"/>
+    <hyperlink ref="J133" r:id="rId207" display="mailto:lawrencerozarioraj_ma2@mail.sjctni.edu" xr:uid="{73E96C0C-7FB2-436A-A715-4F4B32C90710}"/>
+    <hyperlink ref="J132" r:id="rId208" display="mailto:carmel_ma1@mail.sjctni.edu" xr:uid="{FECEDAF0-2060-4749-B60B-A2B74C948947}"/>
+    <hyperlink ref="J131" r:id="rId209" display="mailto:aseervatham_ma1@mail.sjctni.edu" xr:uid="{8CB86664-F516-4B53-AA00-8234387C9D3D}"/>
+    <hyperlink ref="J130" r:id="rId210" display="mailto:arulgnanapragasam_ma1@mail.sjctni.edu" xr:uid="{6B4224B3-20D0-454A-B9D2-9259DAA5FCEE}"/>
+    <hyperlink ref="J129" r:id="rId211" display="mailto:lenin_ma1@mail.sjctni.edu" xr:uid="{254C4AB7-74F0-489A-BA83-55AC5A8FFAFB}"/>
+    <hyperlink ref="J128" r:id="rId212" display="mailto:amalorpavajerline_ma1@mail.sjctni.edu" xr:uid="{1F04A7EA-5D5F-433D-9B3D-A10BEB463744}"/>
+    <hyperlink ref="J127" r:id="rId213" display="mailto:geethasivaraman_ma1@mail.sjctni.edu" xr:uid="{06591B5F-37C3-49B7-B045-67A9C811AD85}"/>
+    <hyperlink ref="J126" r:id="rId214" display="mailto:vairaperumal_ma1@mail.sjctni.edu" xr:uid="{E0D35E88-C344-455A-B49B-60C547E9491E}"/>
+    <hyperlink ref="J125" r:id="rId215" display="mailto:ithayaezhilmanna_ma1@mail.sjctni.edu" xr:uid="{9E1F6747-98B1-443A-8C2D-FC4E99107D85}"/>
+    <hyperlink ref="J124" r:id="rId216" display="mailto:arockiajeyakumar_ma1@mail.sjctni.edu" xr:uid="{6F88A29A-B470-48A2-8D78-9FE079ADE1B1}"/>
+    <hyperlink ref="J123" r:id="rId217" display="mailto:mariajoseph_ma1@mail.sjctni.edu" xr:uid="{DE6B2903-A87B-40E0-835B-D95547BDDFC8}"/>
+    <hyperlink ref="J122" r:id="rId218" display="mailto:christyroja_ma1@mail.sjctni.edu" xr:uid="{39C2FDF6-957A-4D4C-B167-C6F286F74369}"/>
+    <hyperlink ref="J121" r:id="rId219" display="mailto:praveen_ma1@mail.sjctni.edu" xr:uid="{43208E5C-EEF6-42C8-A7B6-47B2B4EDF75C}"/>
+    <hyperlink ref="J120" r:id="rId220" display="mailto:anthonyeldred_ma1@mail.sjctni.edu" xr:uid="{B1D4AB80-EA5E-4FD1-BE6E-48E45C3E16F7}"/>
+    <hyperlink ref="J119" r:id="rId221" display="mailto:umamaheswari_ma1@mail.sjctni.edu" xr:uid="{5174DF08-E702-485E-BEAD-51FAA9167EF7}"/>
+    <hyperlink ref="J118" r:id="rId222" display="mailto:dominic_ma1@mail.sjctni.edu" xr:uid="{41323CAF-FD04-4336-B3BE-1048353ED732}"/>
+    <hyperlink ref="J117" r:id="rId223" display="mailto:thiagarajan_ma1@mail.sjctni.edu" xr:uid="{A7BC0D85-7061-4717-8208-13FC2733C418}"/>
+    <hyperlink ref="J116" r:id="rId224" xr:uid="{D17DDE0D-B6EA-4121-90E1-216D4D98D7F7}"/>
+    <hyperlink ref="J112" r:id="rId225" display="mailto:nikilprakasht_it2@mail.sjctni.edu" xr:uid="{ADAF7638-A205-45E7-ABED-7C3493880ED4}"/>
+    <hyperlink ref="J111" r:id="rId226" display="mailto:carol_cy2@mail.sjctni.edu" xr:uid="{9BF59017-19DC-4870-9C06-B3E56436ED20}"/>
+    <hyperlink ref="J110" r:id="rId227" display="mailto:richard_it2@mail.sjctni.edu" xr:uid="{7183D95B-1884-46DB-9000-F0C66F57B5EF}"/>
+    <hyperlink ref="J109" r:id="rId228" display="mailto:mangaibegum_cy2@mail.sjctni.edu" xr:uid="{A350E485-E431-4B54-ACF7-6D15DD0F365F}"/>
+    <hyperlink ref="J108" r:id="rId229" display="mailto:venishraja_cy2@mail.sjctni.edu" xr:uid="{51B74FF7-01E2-4693-8B95-9C93C86E1CD8}"/>
+    <hyperlink ref="J107" r:id="rId230" display="mailto:bastinthiyagaraj_cy2@mail.sjctni.edu" xr:uid="{A4E0B506-EF49-4520-8BF1-E3AE2439DD9F}"/>
+    <hyperlink ref="J106" r:id="rId231" display="mailto:mariaantoniatemartin_cy2@mail.sjctni.edu" xr:uid="{36ECB4A9-3A41-4C67-9CAE-CD358757C7B9}"/>
+    <hyperlink ref="J105" r:id="rId232" display="mailto:martin_it2@mail.sjctni.edu" xr:uid="{26A0A58A-ED20-4AB3-A00A-CB4D676B1245}"/>
+    <hyperlink ref="J104" r:id="rId233" display="mailto:antonyprakash_cy2@mail.sjctni.edu" xr:uid="{94AEC252-497F-4A75-86CA-769FB18DC131}"/>
+    <hyperlink ref="J102" r:id="rId234" display="mailto:beatricedorothy_ds2@mail.sjctni.edu" xr:uid="{ABEF7AEF-E4A5-4CDA-BBDA-910C6482657C}"/>
+    <hyperlink ref="J101" r:id="rId235" display="mailto:kriushanth_ds2@mail.sjctni.edu" xr:uid="{B12FA3D5-9552-4D53-A179-66704AC0F1C7}"/>
+    <hyperlink ref="J100" r:id="rId236" xr:uid="{39A1A6CA-822F-400E-994F-E1E36F78620C}"/>
+    <hyperlink ref="J99" r:id="rId237" display="mailto:rajaretnam_ds2@mail.sjctni.edu" xr:uid="{A24D0589-3D7A-4E6E-A264-C684553F5FD4}"/>
+    <hyperlink ref="J96" r:id="rId238" xr:uid="{61BC2AC1-63A9-4F8F-AC31-603C65B54F84}"/>
+    <hyperlink ref="J95" r:id="rId239" xr:uid="{C90445A0-51D4-43CB-A2BC-F8F158E85B1B}"/>
+    <hyperlink ref="J94" r:id="rId240" xr:uid="{9C32B9ED-F2CB-4BB5-9D28-D7A1F77951B3}"/>
+    <hyperlink ref="J93" r:id="rId241" xr:uid="{CBFEBBF1-EE15-45E1-BD65-5D71F79D6294}"/>
+    <hyperlink ref="J92" r:id="rId242" xr:uid="{2E14F8F6-D3E8-439F-B9E7-47B77FF35515}"/>
+    <hyperlink ref="J91" r:id="rId243" xr:uid="{B013F430-581A-453F-9FC7-0A4F8B7E9CDA}"/>
+    <hyperlink ref="J90" r:id="rId244" xr:uid="{D607720E-B4D2-4A71-AF89-9083D504C8FA}"/>
+    <hyperlink ref="J89" r:id="rId245" xr:uid="{93AF7A9D-BFB1-433B-AF8B-A51C1C1FD66F}"/>
+    <hyperlink ref="J88" r:id="rId246" xr:uid="{C2FA638B-067D-4805-8834-D8BD9F57E8C3}"/>
+    <hyperlink ref="J87" r:id="rId247" xr:uid="{F6AA06D5-F198-41F4-96F5-99F5231B71DD}"/>
+    <hyperlink ref="J86" r:id="rId248" xr:uid="{B4D56B07-6B58-44F6-B49F-535BF52A1869}"/>
+    <hyperlink ref="J85" r:id="rId249" xr:uid="{A7D3CD70-B34C-47FA-BDFD-73A5F50C79CD}"/>
+    <hyperlink ref="J84" r:id="rId250" xr:uid="{DDF9737F-DC21-423F-B7A8-99B3C32A32EC}"/>
+    <hyperlink ref="J83" r:id="rId251" xr:uid="{92A15F20-F04A-4F3E-A87C-03CAA937AA09}"/>
+    <hyperlink ref="J82" r:id="rId252" xr:uid="{5A59712E-C3DE-4A19-A8E8-C80AD15825A5}"/>
+    <hyperlink ref="J81" r:id="rId253" xr:uid="{D806A201-4DA8-42E6-BB02-93B65DDC61EE}"/>
+    <hyperlink ref="J80" r:id="rId254" xr:uid="{B784CC6B-ACA3-4A27-9EA5-02C761DCC28A}"/>
+    <hyperlink ref="J79" r:id="rId255" xr:uid="{CA1737B2-3F6F-407A-95FF-3E406CD81462}"/>
+    <hyperlink ref="J78" r:id="rId256" xr:uid="{17997236-0A0E-44A3-97BB-CD184BF4D697}"/>
+    <hyperlink ref="J77" r:id="rId257" xr:uid="{8CECA54A-A9FD-4DCA-B7DC-8687CFAF56B2}"/>
+    <hyperlink ref="J76" r:id="rId258" xr:uid="{FBF18AD3-14FF-4040-9D0D-E946595BD5AE}"/>
+    <hyperlink ref="J73" r:id="rId259" display="mailto:banumathi_ss1@mail.sjctni.edu" xr:uid="{D2664550-8230-4530-A353-B25EE0D9724D}"/>
+    <hyperlink ref="J72" r:id="rId260" display="mailto:janeva_ss1@mail.sjctni.edu" xr:uid="{D54C57E8-A68A-470C-90A3-E461BE46F4F2}"/>
+    <hyperlink ref="J71" r:id="rId261" display="mailto:genocinthia_ss1@mail.sjctni.edu" xr:uid="{E026B3D1-B944-43A1-B69A-FB0C03EEEEAB}"/>
+    <hyperlink ref="J69" r:id="rId262" xr:uid="{EE424ED9-F8D5-4B02-BB15-930578A44E11}"/>
+    <hyperlink ref="J66" r:id="rId263" xr:uid="{92812536-E14D-4695-8550-4A4684C2568B}"/>
+    <hyperlink ref="J65" r:id="rId264" xr:uid="{B0C41A4E-2D1B-41E2-9897-24CEFF2411E3}"/>
+    <hyperlink ref="J64" r:id="rId265" xr:uid="{C092E216-7F24-4F5C-AD8A-B38CEAB94A60}"/>
+    <hyperlink ref="J62" r:id="rId266" display="mailto:jerryrichards_cr2@mail.sjctni.edu" xr:uid="{3BF963B7-DBDE-4D7D-A7CA-B44AAAD62FFE}"/>
+    <hyperlink ref="J61" r:id="rId267" display="mailto:prabakaran_cr2@mail.sjctni.edu" xr:uid="{EBB06740-E339-4F9F-B639-15EE28DCA6D9}"/>
+    <hyperlink ref="J13" r:id="rId268" display="mailto:sahayasathish_bo1@mail.sjctni.edu" xr:uid="{40BF0A23-5B55-46B5-81B6-0C78B594CB65}"/>
+    <hyperlink ref="J12" r:id="rId269" xr:uid="{A196ADF3-3394-4FA6-B81F-C52F701897B9}"/>
+    <hyperlink ref="J11" r:id="rId270" xr:uid="{F5E43E46-2D93-416E-9527-CC138B4CEE73}"/>
+    <hyperlink ref="J10" r:id="rId271" xr:uid="{1D146766-B07E-452D-A0DE-679A8F07671E}"/>
+    <hyperlink ref="J9" r:id="rId272" xr:uid="{FCEB218A-35CB-46B5-B07E-EB292E601D02}"/>
+    <hyperlink ref="J8" r:id="rId273" xr:uid="{A7B9D8D4-619D-4208-9079-636944F6B4F0}"/>
+    <hyperlink ref="J7" r:id="rId274" xr:uid="{7374DC9D-C649-4289-9A58-4BF6E28A0F6A}"/>
+    <hyperlink ref="J5" r:id="rId275" xr:uid="{3B9C7A78-8E3A-4E1A-9EC1-C24351124236}"/>
+    <hyperlink ref="J6" r:id="rId276" display="mailto:geegi_bi2@mail.sjctni.edu" xr:uid="{A08901E5-BD66-41EF-9D30-BB9688C3CF53}"/>
+    <hyperlink ref="J4" r:id="rId277" xr:uid="{A14BB14D-6583-4E33-9CB5-845942840D30}"/>
+    <hyperlink ref="J23" r:id="rId278" display="mailto:bastinchurchill_bo1@mail.sjctni.edu" xr:uid="{D1B933E7-D7C5-49BD-A272-B4D47584BA96}"/>
+    <hyperlink ref="J22" r:id="rId279" display="mailto:anusuya_bo1@mail.sjctni.edu" xr:uid="{0A1445A1-76DC-4D4C-ABC5-A9BA36BCDD53}"/>
+    <hyperlink ref="J21" r:id="rId280" display="mailto:jktagore_bo1@mail.sjctni.edu" xr:uid="{3B4C2487-A290-47DC-BCF3-138BDA501E12}"/>
+    <hyperlink ref="J20" r:id="rId281" display="mailto:davidraja_bo1@mail.sjctni.edu" xr:uid="{C50EA119-02AA-4DF8-8FB2-E717F6D79235}"/>
+    <hyperlink ref="J19" r:id="rId282" display="mailto:johnpeterarulanandam_bo1@mail.sjctni.edu" xr:uid="{1C770BDC-DB3F-4F65-B81F-9AE8CA950210}"/>
+    <hyperlink ref="J18" r:id="rId283" display="mailto:francissathiyaseelan_bo1@mail.sjctni.edu" xr:uid="{31490BCB-CF27-4622-AFFF-796D034A5379}"/>
+    <hyperlink ref="J17" r:id="rId284" display="mailto:francisxavier_bo1@mail.sjctni.edu" xr:uid="{03DA3A05-46C5-496C-9D74-EC67A68CFA94}"/>
+    <hyperlink ref="J16" r:id="rId285" display="mailto:soosairaj_bo1@mail.sjctni.edu" xr:uid="{BB341FF9-6352-4D37-9EC4-F60D9999F099}"/>
+    <hyperlink ref="J15" r:id="rId286" display="mailto:egbertselwinrose_bo1@mail.sjctni.edu" xr:uid="{C6135AC3-71F3-4230-ACC5-1050601C87A6}"/>
+    <hyperlink ref="J14" r:id="rId287" display="mailto:senthilkumar_bo1@mail.sjctni.edu" xr:uid="{1F658893-B83F-407A-819D-BE536F1BE588}"/>
+    <hyperlink ref="J136" r:id="rId288" display="mailto:jairoselin_ma2@mail.sjctni.edu" xr:uid="{511CCE8C-EF96-473E-8599-2C03DFBD8A20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId289"/>
